--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0 - Indice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 - Parametri" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 - BTP Italia Si" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 - BTP Italia classico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4 - BTP Valore" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5 - BTP Futura" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6 - BTP nominali" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7 - MATRICE COMPARATIVA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8 - Break-even" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 - Indice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 - Parametri" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - BTP Italia Si" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 - BTP Italia classico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 - BTP Valore" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 - BTP Futura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 - BTP nominali" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 - MATRICE COMPARATIVA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 - Break-even" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -279,14 +279,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -311,7 +311,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -352,7 +352,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -363,8 +363,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -404,14 +404,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -436,7 +436,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -477,7 +477,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -488,8 +488,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -529,14 +529,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -561,7 +561,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -602,7 +602,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -613,8 +613,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -654,14 +654,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -686,7 +686,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -727,7 +727,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -738,8 +738,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -779,14 +779,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -810,14 +810,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -846,8 +846,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -884,7 +884,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -895,8 +895,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -936,14 +936,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -967,7 +967,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="10B981"/>
               </a:solidFill>
@@ -977,7 +977,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1002,7 +1002,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="1E40AF"/>
               </a:solidFill>
@@ -1012,7 +1012,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1037,7 +1037,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="F59E0B"/>
               </a:solidFill>
@@ -1047,7 +1047,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1072,7 +1072,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="EF4444"/>
               </a:solidFill>
@@ -1082,7 +1082,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1107,7 +1107,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="8B5CF6"/>
               </a:solidFill>
@@ -1117,7 +1117,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1146,8 +1146,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1184,7 +1184,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1195,8 +1195,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1236,14 +1236,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1268,7 +1268,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1309,7 +1309,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1320,8 +1320,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1361,14 +1361,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="11"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1393,10 +1393,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="10B981"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1420,10 +1420,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E40AF"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1447,10 +1447,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="F59E0B"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1474,10 +1474,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="EF4444"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1501,10 +1501,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="8B5CF6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1546,7 +1546,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1557,8 +1557,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1598,14 +1598,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1630,7 +1630,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1671,7 +1671,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="4500">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1682,8 +1682,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1738,9 +1738,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1750,7 +1750,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1765,9 +1765,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1777,7 +1777,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1792,9 +1792,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1804,7 +1804,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1819,9 +1819,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1831,7 +1831,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1846,9 +1846,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1858,7 +1858,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1873,9 +1873,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1885,7 +1885,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1900,9 +1900,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1912,7 +1912,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1927,9 +1927,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1939,7 +1939,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1954,9 +1954,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
@@ -3563,7 +3563,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Default classico 1,6% sul prospetto, a prezzo 102 con 5y residui → YTM ~1,2% reale.</t>
+          <t>Default classico 1,6% sul prospetto, a prezzo 102 con 4y residui → YTM ~1,1% reale.</t>
         </is>
       </c>
     </row>
@@ -5211,19 +5211,19 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>'1 - Parametri'!B5*(1-'1 - Parametri'!B8)+('1 - Parametri'!B7)/5*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B37)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>'1 - Parametri'!B5*(1-'1 - Parametri'!B8)+('1 - Parametri'!B7)/5*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B38)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'1 - Parametri'!B5*(1-'1 - Parametri'!B8)+('1 - Parametri'!B7)/5*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B39)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'1 - Parametri'!B5*(1-'1 - Parametri'!B8)+('1 - Parametri'!B7)/5*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B40)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)</f>
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)</f>
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)</f>
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)</f>
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Soglia infl. break-even</t>
+          <t>Soglia infl. break-even (lorda)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -5473,7 +5473,7 @@
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>C6-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B6-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E6" s="21">
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>C7-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B7-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E7" s="21">
@@ -5519,7 +5519,7 @@
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>C8-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B8-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E8" s="21">
@@ -5542,7 +5542,7 @@
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>C9-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B9-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E9" s="21">
@@ -5565,7 +5565,7 @@
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>C10-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B10-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E10" s="21">
@@ -5588,7 +5588,7 @@
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>C11-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B11-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E11" s="21">
@@ -5611,7 +5611,7 @@
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>C12-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)*(1-'1 - Parametri'!B8)</f>
+        <f>B12-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
       <c r="E12" s="21">

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0 - Indice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 - Parametri" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - BTP Italia Si" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 - BTP Italia classico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 - BTP Valore" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 - BTP Futura" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 - BTP nominali" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 - MATRICE COMPARATIVA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 - Break-even" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="0 - Indice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1 - Parametri" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 - BTP Italia Si" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3 - BTP Italia classico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4 - BTP Valore" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5 - BTP Futura" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6 - BTP nominali" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7 - MATRICE COMPARATIVA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8 - Break-even" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,9 +26,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -141,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,6 +193,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -279,14 +283,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -311,7 +315,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -352,7 +356,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -363,8 +367,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -404,14 +408,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -436,7 +440,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -477,7 +481,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -488,8 +492,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -529,14 +533,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -561,7 +565,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -602,7 +606,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -613,8 +617,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -654,14 +658,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -686,7 +690,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -727,7 +731,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -738,8 +742,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -779,14 +783,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -810,14 +814,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -846,8 +850,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -884,7 +888,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -895,8 +899,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -936,14 +940,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -967,7 +971,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="10B981"/>
               </a:solidFill>
@@ -977,7 +981,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1002,7 +1006,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="1E40AF"/>
               </a:solidFill>
@@ -1012,7 +1016,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1037,7 +1041,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="F59E0B"/>
               </a:solidFill>
@@ -1047,7 +1051,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1072,7 +1076,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="EF4444"/>
               </a:solidFill>
@@ -1082,7 +1086,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1107,7 +1111,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="8B5CF6"/>
               </a:solidFill>
@@ -1117,7 +1121,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1146,8 +1150,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1184,7 +1188,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1195,8 +1199,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1236,14 +1240,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1268,7 +1272,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1309,7 +1313,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1320,8 +1324,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1361,14 +1365,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="11"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1393,10 +1397,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="10B981"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1420,10 +1424,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E40AF"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1447,10 +1451,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="F59E0B"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1474,10 +1478,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EF4444"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1501,10 +1505,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="8B5CF6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1546,7 +1550,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1557,8 +1561,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1598,14 +1602,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1630,7 +1634,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1671,7 +1675,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="4500">
+            <a:ln w="4500">
               <a:solidFill>
                 <a:srgbClr val="D0D0D0"/>
               </a:solidFill>
@@ -1682,8 +1686,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1723,7 +1727,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1738,9 +1742,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1750,7 +1754,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1765,9 +1769,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1777,7 +1781,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1792,9 +1796,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1804,7 +1808,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1819,9 +1823,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1831,7 +1835,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1846,9 +1850,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1858,7 +1862,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1873,9 +1877,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1885,7 +1889,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -1900,9 +1904,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1912,7 +1916,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1927,9 +1931,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1939,7 +1943,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1954,9 +1958,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2599,19 +2603,19 @@
           <t>Giovane 25-34</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="23" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="23" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2621,19 +2625,19 @@
           <t>Mezza età 35-49</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="23" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -2643,19 +2647,19 @@
           <t>Over 50 pre-FIRE</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>0.3</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="23" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2665,19 +2669,19 @@
           <t>FIRE in decumulo</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="23" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
           <t>Tua aliquota IRPEF marginale (info)</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="24" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -2850,10 +2854,10 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
-        <v/>
-      </c>
-      <c r="C12" s="21">
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
+        <v/>
+      </c>
+      <c r="C12" s="22">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2861,14 +2865,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>BTP Italia clas.</t>
+          <t>BTP Italia clas. (YTM MOT)</t>
         </is>
       </c>
       <c r="B13" s="16">
-        <f>'1 - Parametri'!B12*(1-'1 - Parametri'!B8)</f>
-        <v/>
-      </c>
-      <c r="C13" s="21">
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="22">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2880,10 +2884,10 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>(1+((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+'1 - Parametri'!B18/6)*(1-'1 - Parametri'!B8))/(1+B7)-1</f>
-        <v/>
-      </c>
-      <c r="C14" s="21">
+        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+'1 - Parametri'!B18/6)*(1-'1 - Parametri'!B8)-B7</f>
+        <v/>
+      </c>
+      <c r="C14" s="22">
         <f>IF(B6&gt;=6,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2895,10 +2899,10 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>(1+'1 - Parametri'!B32*(1-'1 - Parametri'!B8))/(1+B7)-1</f>
-        <v/>
-      </c>
-      <c r="C15" s="21">
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-B7</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2910,10 +2914,10 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>(1+'1 - Parametri'!B34*(1-'1 - Parametri'!B8))/(1+B7)-1</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
+        <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-B7</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
         <f>IF(B6&gt;=10,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2931,7 +2935,7 @@
           <t>Miglior strumento</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="22">
         <f>INDEX(A12:A16,MATCH(MAX(B12:B16),B12:B16,0))</f>
         <v/>
       </c>
@@ -2997,7 +3001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3592,10 +3596,51 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>YTM reale NETTO (citati nel video)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>YTM reale NETTO mag 2028</t>
+        </is>
+      </c>
+      <c r="B59" s="16">
+        <f>B50*(1-B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>YTM reale NETTO giu 2030</t>
+        </is>
+      </c>
+      <c r="B60" s="16">
+        <f>B52*(1-B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>YTM reale NETTO medio (2 ISIN)</t>
+        </is>
+      </c>
+      <c r="B61" s="16">
+        <f>B56*(1-B8)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A21:D21"/>
@@ -3621,7 +3666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3629,6 +3674,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -3863,7 +3909,12 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>IRR netto annuo</t>
+          <t>IRR nom netto annuo (lineare)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>IRR reale netto</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3937,11 @@
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>((D20+$B$9)/$B$9)^(1/$B$6)-1</f>
+        <f>ROUND(($B$5+$B$7/$B$6+B13)*(1-$B$8),6)</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f>E20-B13</f>
         <v/>
       </c>
     </row>
@@ -3909,7 +3964,11 @@
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>((D21+$B$9)/$B$9)^(1/$B$6)-1</f>
+        <f>ROUND(($B$5+$B$7/$B$6+B14)*(1-$B$8),6)</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>E21-B14</f>
         <v/>
       </c>
     </row>
@@ -3932,7 +3991,11 @@
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>((D22+$B$9)/$B$9)^(1/$B$6)-1</f>
+        <f>ROUND(($B$5+$B$7/$B$6+B15)*(1-$B$8),6)</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>E22-B15</f>
         <v/>
       </c>
     </row>
@@ -3955,7 +4018,11 @@
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>((D23+$B$9)/$B$9)^(1/$B$6)-1</f>
+        <f>ROUND(($B$5+$B$7/$B$6+B16)*(1-$B$8),6)</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>E23-B16</f>
         <v/>
       </c>
     </row>
@@ -4501,7 +4568,7 @@
         <f>B5</f>
         <v/>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="21">
         <f>B5*(1-$B$10)</f>
         <v/>
       </c>
@@ -4524,7 +4591,7 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="21">
         <f>B6*(1-$B$10)</f>
         <v/>
       </c>
@@ -4547,7 +4614,7 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="21">
         <f>B7*(1-$B$10)</f>
         <v/>
       </c>
@@ -4603,11 +4670,11 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>IRR netto annuo</t>
+          <t>IRR nom netto annuo (lineare)</t>
         </is>
       </c>
       <c r="B23" s="16">
-        <f>((B22+B11)/B11)^(1/B9)-1</f>
+        <f>ROUND(((B5+B6+B7)/3+B8/B9)*(1-B10),6)</f>
         <v/>
       </c>
     </row>
@@ -4646,7 +4713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4654,6 +4721,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -4798,6 +4866,11 @@
           <t>Tot. netto 12y</t>
         </is>
       </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>IRR nom netto annuo (lineare)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -4820,6 +4893,10 @@
         <f>D16+$B$12*C16*(1-$B$11)</f>
         <v/>
       </c>
+      <c r="F16" s="16">
+        <f>E16/$B$12/$B$10</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -4842,6 +4919,10 @@
         <f>D17+$B$12*C17*(1-$B$11)</f>
         <v/>
       </c>
+      <c r="F17" s="16">
+        <f>E17/$B$12/$B$10</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -4862,6 +4943,10 @@
       </c>
       <c r="E18" s="19">
         <f>D18+$B$12*C18*(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>E18/$B$12/$B$10</f>
         <v/>
       </c>
     </row>
@@ -4965,7 +5050,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>IRR netto annuo</t>
+          <t>Cedola netta annua EUR</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5093,7 @@
         <f>'1 - Parametri'!B30</f>
         <v/>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="21">
         <f>B9*(1-$B$6)</f>
         <v/>
       </c>
@@ -5016,8 +5101,8 @@
         <f>$B$7*C9*2</f>
         <v/>
       </c>
-      <c r="E9" s="16">
-        <f>C9</f>
+      <c r="E9" s="19">
+        <f>$B$7*C9</f>
         <v/>
       </c>
     </row>
@@ -5031,7 +5116,7 @@
         <f>'1 - Parametri'!B31</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="21">
         <f>B10*(1-$B$6)</f>
         <v/>
       </c>
@@ -5039,8 +5124,8 @@
         <f>$B$7*C10*3</f>
         <v/>
       </c>
-      <c r="E10" s="16">
-        <f>C10</f>
+      <c r="E10" s="19">
+        <f>$B$7*C10</f>
         <v/>
       </c>
     </row>
@@ -5054,7 +5139,7 @@
         <f>'1 - Parametri'!B32</f>
         <v/>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="21">
         <f>B11*(1-$B$6)</f>
         <v/>
       </c>
@@ -5062,8 +5147,8 @@
         <f>$B$7*C11*5</f>
         <v/>
       </c>
-      <c r="E11" s="16">
-        <f>C11</f>
+      <c r="E11" s="19">
+        <f>$B$7*C11</f>
         <v/>
       </c>
     </row>
@@ -5077,7 +5162,7 @@
         <f>'1 - Parametri'!B33</f>
         <v/>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="21">
         <f>B12*(1-$B$6)</f>
         <v/>
       </c>
@@ -5085,8 +5170,8 @@
         <f>$B$7*C12*7</f>
         <v/>
       </c>
-      <c r="E12" s="16">
-        <f>C12</f>
+      <c r="E12" s="19">
+        <f>$B$7*C12</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5185,7 @@
         <f>'1 - Parametri'!B34</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="21">
         <f>B13*(1-$B$6)</f>
         <v/>
       </c>
@@ -5108,8 +5193,8 @@
         <f>$B$7*C13*10</f>
         <v/>
       </c>
-      <c r="E13" s="16">
-        <f>C13</f>
+      <c r="E13" s="19">
+        <f>$B$7*C13</f>
         <v/>
       </c>
     </row>
@@ -5211,19 +5296,19 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B37)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B37)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37,6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B38)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B38)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38,6)</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B39)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B39)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39,6)</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B40)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B40)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40,6)</f>
         <v/>
       </c>
     </row>
@@ -5257,19 +5342,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>(1+((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B37)-1</f>
+        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(1+((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B38)-1</f>
+        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(1+((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B39)-1</f>
+        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(1+((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B40)-1</f>
+        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
@@ -5280,19 +5365,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>(1+'1 - Parametri'!B32*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B37)-1</f>
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(1+'1 - Parametri'!B32*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B38)-1</f>
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(1+'1 - Parametri'!B32*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B39)-1</f>
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(1+'1 - Parametri'!B32*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B40)-1</f>
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
@@ -5303,19 +5388,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>(1+'1 - Parametri'!B34*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B37)-1</f>
+        <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>(1+'1 - Parametri'!B34*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B38)-1</f>
+        <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>(1+'1 - Parametri'!B34*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B39)-1</f>
+        <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>(1+'1 - Parametri'!B34*(1-'1 - Parametri'!B8))/(1+'1 - Parametri'!B40)-1</f>
+        <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
@@ -5476,8 +5561,8 @@
         <f>B6-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E6" s="21">
-        <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D6*100,1)&amp;"%"))</f>
+      <c r="E6" s="22">
+        <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D6*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5499,8 +5584,8 @@
         <f>B7-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E7" s="21">
-        <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D7*100,1)&amp;"%"))</f>
+      <c r="E7" s="22">
+        <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D7*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5522,8 +5607,8 @@
         <f>B8-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E8" s="21">
-        <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D8*100,1)&amp;"%"))</f>
+      <c r="E8" s="22">
+        <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D8*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5545,8 +5630,8 @@
         <f>B9-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E9" s="21">
-        <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D9*100,1)&amp;"%"))</f>
+      <c r="E9" s="22">
+        <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D9*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5568,8 +5653,8 @@
         <f>B10-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E10" s="21">
-        <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D10*100,1)&amp;"%"))</f>
+      <c r="E10" s="22">
+        <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D10*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5591,8 +5676,8 @@
         <f>B11-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E11" s="21">
-        <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D11*100,1)&amp;"%"))</f>
+      <c r="E11" s="22">
+        <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D11*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5614,8 +5699,8 @@
         <f>B12-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E12" s="21">
-        <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D12*100,1)&amp;"%"))</f>
+      <c r="E12" s="22">
+        <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D12*100,2)&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -5634,17 +5719,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Cedola reale</t>
+          <t>YTM reale NETTO (MOT)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Cedola reale Sì</t>
+          <t>Sì reale netto</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Gap reale (vs Sì)</t>
+          <t>Vantaggio Sì (pp)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -5660,19 +5745,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>'1 - Parametri'!B50</f>
+        <f>'1 - Parametri'!B50*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>'1 - Parametri'!B5</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>IF(D16&lt;=0,"Sì vince a parità infl.","Sì NON raggiunge (gap reale "&amp;ROUND(D16*100,1)&amp;"pp)")</f>
+        <f>C16-B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>IF(D16&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D16*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D16*100,2)&amp;"pp)")</f>
         <v/>
       </c>
     </row>
@@ -5683,19 +5768,42 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>'1 - Parametri'!B52</f>
+        <f>'1 - Parametri'!B52*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>'1 - Parametri'!B5</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>IF(D17&lt;=0,"Sì vince a parità infl.","Sì NON raggiunge (gap reale "&amp;ROUND(D17*100,1)&amp;"pp)")</f>
+        <f>C17-B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>IF(D17&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D17*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D17*100,2)&amp;"pp)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>BTP Italia classico MEDIA 2 ISIN (YTM reale NETTO medio)</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>C18-B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>IF(D18&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D18*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D18*100,2)&amp;"pp)")</f>
         <v/>
       </c>
     </row>
@@ -5734,15 +5842,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D17">
+  <conditionalFormatting sqref="D16:D18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="00F87171"/>
+        <color rgb="00FEF3C7"/>
         <color rgb="0086EFAC"/>
-        <color rgb="00FEF3C7"/>
-        <color rgb="00F87171"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -4048,7 +4048,7 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="E20:E23">
     <cfRule type="colorScale" priority="1">
@@ -4970,8 +4970,8 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <conditionalFormatting sqref="E16:E18">
     <cfRule type="colorScale" priority="1">

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -1730,7 +1730,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -1811,7 +1811,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -4042,13 +4042,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="E20:E23">
     <cfRule type="colorScale" priority="1">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Sul secondario disponibili 4 ISIN ma cedole molto basse (0,35-1,0%). Confronto utile per capire la LOGICA del premio fedelta', non per acquisto attuale. Struttura step-up 4+4+4 anni (1-4: 0,35%, 5-8: 0,60%, 9-12: 1,00%).</t>
@@ -4966,12 +4966,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="E16:E18">
     <cfRule type="colorScale" priority="1">

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,6 +182,9 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -195,6 +198,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -284,7 +290,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -409,7 +414,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -534,7 +538,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -659,7 +662,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -784,7 +786,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -941,7 +942,6 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -1078,7 +1078,7 @@
           <spPr>
             <a:ln w="28000">
               <a:solidFill>
-                <a:srgbClr val="EF4444"/>
+                <a:srgbClr val="0EA5E9"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1113,6 +1113,41 @@
           <spPr>
             <a:ln w="28000">
               <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'7 - MATRICE COMPARATIVA'!$B$5:$E$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'7 - MATRICE COMPARATIVA'!$B$10:$E$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'7 - MATRICE COMPARATIVA'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
                 <a:srgbClr val="8B5CF6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
@@ -1133,7 +1168,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'7 - MATRICE COMPARATIVA'!$B$10:$E$10</f>
+              <f>'7 - MATRICE COMPARATIVA'!$B$11:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -1241,7 +1276,6 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1366,7 +1400,6 @@
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -1603,7 +1636,6 @@
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2258,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2318,7 +2350,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Capitale rivalutato + cedola reale 2,0%</t>
+          <t>Capitale rivalutato + cedola reale 1,6% (giu 2030)</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Step-up 2+2+2 + premio 0,8%</t>
+          <t>Step-up 2,60/3,20/3,80 + YTM a prezzo MOT 98,65</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2374,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Storico 4a emissione + premio PIL</t>
+          <t>Storico 4a emissione + YTM a prezzo MOT 86,15</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2398,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>5 strumenti x 4 scenari (rendimenti REALI netti)</t>
+          <t>6 strumenti x 4 scenari (rendimenti REALI netti)</t>
         </is>
       </c>
     </row>
@@ -2458,61 +2490,68 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>• MEF - BTP Italia maggio 2028 (IT0005***) tasso reale 2,0%; giu 2030 (IT0005497000) tasso reale 1,6%</t>
+          <t>• MEF - BTP Italia marzo 2028 (IT0005532723, scad. 14/03/2028) tasso reale 2,0%; giugno 2030 (IT0005497000) tasso reale 1,6%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>• MEF - BTP Valore marzo 2026 step-up 2,60/2,80/3,80% + premio 0,8%, scadenza 10 ott 2032</t>
+          <t>• MEF - BTP Valore marzo 2026 (IT0005696338) step-up DEFINITIVI 2,60/3,20/3,80% + premio 0,8%, scadenza 10 mar 2032</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>• MEF - BTP Futura 4a emissione 2021 (nov 2021), 12 anni step-up 0,35/0,60/1,00 + premio PIL 0,4-3%</t>
+          <t>• MEF - BTP Futura 4a emissione nov 2021 (IT0005466351), 12 anni step-up DEFINITIVI 0,75/1,35/1,70% + doppio premio PIL (solo sottoscrittori originali), scadenza 16 nov 2033</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>• MEF Tesoro - Calendario aste BTP nominali maggio 2026 (asta 13 e 28 maggio)</t>
+          <t>• Borsa Italiana MOT - prezzi ufficiali 09/06/2026: mar 2028 101,97; giu 2030 101,92; Valore 98,65; Futura 86,15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>• Banca d'Italia - Risultati aste BTP nominali 2026 (rendimenti curva 2y-10y)</t>
+          <t>• MEF Tesoro - Calendario aste BTP nominali maggio 2026 (asta 13 e 28 maggio)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>• ISTAT - Indice FOI per famiglie operai e impiegati (escluso tabacchi) - meccanismo BTP Italia</t>
+          <t>• Banca d'Italia - Risultati aste BTP nominali 2026 (rendimenti curva 2y-10y)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>• Eurostat - HICP eurozona per BTPi (non incluso in matrice; alternativa istituzionale)</t>
+          <t>• ISTAT - Indice FOI per famiglie operai e impiegati (escluso tabacchi) - meccanismo BTP Italia</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>• Eurostat - HICP eurozona per BTPi (non incluso in matrice; alternativa istituzionale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>• Borsa Italiana MOT - mercato secondario BTP retail (liquidita' supportata da Dealer MEF)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Aggiornamenti: github.com/marcofire-it/marco-fire-simulatori</t>
         </is>
@@ -2566,32 +2605,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Profilo</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>BTP Italia Si</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>BTP Italia clas.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>BTP Valore</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>BTP nominale 5y</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>BTP nominale 10y</t>
         </is>
@@ -2603,19 +2642,19 @@
           <t>Giovane 25-34</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="25" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2625,19 +2664,19 @@
           <t>Mezza età 35-49</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="25" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -2647,19 +2686,19 @@
           <t>Over 50 pre-FIRE</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="25" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2669,19 +2708,19 @@
           <t>FIRE in decumulo</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="25" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2819,7 +2858,7 @@
           <t>Tua aliquota IRPEF marginale (info)</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="26" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -2831,17 +2870,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Strumento</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Rend. reale annuo</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Idoneo al tuo orizzonte</t>
         </is>
@@ -2857,7 +2896,7 @@
         <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="24">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2872,7 +2911,7 @@
         <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
         <v/>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="24">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2880,14 +2919,14 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>BTP Valore</t>
+          <t>BTP Valore (YTM MOT)</t>
         </is>
       </c>
       <c r="B14" s="16">
-        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+'1 - Parametri'!B18/6)*(1-'1 - Parametri'!B8)-B7</f>
-        <v/>
-      </c>
-      <c r="C14" s="22">
+        <f>'4 - BTP Valore'!B32*(1-'1 - Parametri'!B8)-B7</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
         <f>IF(B6&gt;=6,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2902,7 +2941,7 @@
         <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-B7</f>
         <v/>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="24">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2917,7 +2956,7 @@
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-B7</f>
         <v/>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="24">
         <f>IF(B6&gt;=10,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -2935,7 +2974,7 @@
           <t>Miglior strumento</t>
         </is>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="24">
         <f>INDEX(A12:A16,MATCH(MAX(B12:B16),B12:B16,0))</f>
         <v/>
       </c>
@@ -2957,7 +2996,7 @@
           <t>Valore finale (con cap. + reale)</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>B5*(1+B20)^B6</f>
         <v/>
       </c>
@@ -3001,7 +3040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3038,7 +3077,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
@@ -3098,10 +3137,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>BTP Italia mag 2028 - cedola reale annua</t>
+          <t>BTP Italia mar 2028 - cedola reale annua</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -3109,7 +3148,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>MEF IT0005***: tasso reale 2,0% sul prospetto (rendimento per chi compra a 100)</t>
+          <t>MEF IT0005532723, scadenza 14/03/2028: tasso reale 2,0% sul prospetto (rendimento per chi compra a 100). NB: il titolo e' MARZO 2028, la serie 'mag 2028' non esiste.</t>
         </is>
       </c>
     </row>
@@ -3124,14 +3163,14 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>MEF IT0005497000: tasso reale 1,6% sul prospetto</t>
+          <t>MEF IT0005497000, scadenza 28/06/2030: tasso reale 1,6% sul prospetto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>BTP Valore (ultima emissione marzo 2026, secondario)</t>
+          <t>BTP Valore (7a emissione marzo 2026, ISIN IT0005696338, secondario)</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3185,22 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>MEF: 2,60% (cedole trimestrali)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+          <t>MEF: 2,60% definitivo (cedole trimestrali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 3-4</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>MEF: 2,80%</t>
+          <t>MEF: 3,20% definitivo (il 2,80 era il minimo garantito pre-collocamento)</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3219,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta'</t>
@@ -3191,7 +3230,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>MEF: 0,8% del capitale a scadenza</t>
+          <t>MEF: 0,8% del capitale a scadenza (solo sottoscrittori in collocamento)</t>
         </is>
       </c>
     </row>
@@ -3206,29 +3245,29 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Scadenza 10 ott 2032</t>
+          <t>Scadenza 10 mar 2032</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>BTP Futura (sospeso, riferimento storico)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+          <t>BTP Futura 4a emissione nov 2021 (sospeso, ISIN IT0005466351 sul MOT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 1-4</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.0035</v>
+        <v>0.0075</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Storico 4a emissione nov 2021: 0,35%</t>
+          <t>MEF 4a emissione nov 2021, step DEFINITIVI: 0,75% (NON 0,35 = 2a emissione)</t>
         </is>
       </c>
     </row>
@@ -3239,11 +3278,11 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.006</v>
+        <v>0.0135</v>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Storico: 0,60% (anni 5-8)</t>
+          <t>MEF definitivo: 1,35% (anni 5-8)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3293,15 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Storico: 1,00% (anni 9-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+          <t>MEF definitivo: 1,70% (anni 9-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta' min (PIL)</t>
@@ -3273,11 +3312,11 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Floor 0,4% se PIL nominale basso</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>Floor 0,4% se PIL nominale basso (solo sottoscrittori originali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta' max (PIL)</t>
@@ -3288,11 +3327,11 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Cap 3,0% se PIL nominale alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+          <t>Cap 3,0% se PIL nominale alto (solo sottoscrittori originali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Durata (anni)</t>
@@ -3303,7 +3342,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Storica 4a emissione (4+4+4 step-up)</t>
+          <t>4a emissione (4+4+4 step-up), scadenza 16/11/2033</t>
         </is>
       </c>
     </row>
@@ -3488,11 +3527,11 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Prezzo secondario BTP Italia mag 2028</t>
+          <t>Prezzo secondario BTP Italia mar 2028</t>
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>104</v>
+        <v>101.97</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -3500,13 +3539,13 @@
         </is>
       </c>
       <c r="D46" s="15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Quotazione corrente sul MOT (100 = par). Aggiorna col valore reale al 12/06/2026. Default 104 = premio 4% (stima 2026 con tassi sopra cedola del prospetto).</t>
+          <t>Quotazione ufficiale MOT 09/06/2026: 101,97 (100 = par). Aggiorna col valore corrente quando cambia il mercato.</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3556,7 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>102</v>
+        <v>101.92</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
@@ -3531,14 +3570,14 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Default 102 = premio 2%. Aggiorna col valore reale al 12/06/2026.</t>
+          <t>Quotazione ufficiale MOT 09/06/2026: 101,92. Aggiorna col valore corrente quando cambia il mercato.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>YTM reale mag 2028 (per chi compra al MOT oggi)</t>
+          <t>YTM reale mar 2028 (per chi compra al MOT oggi)</t>
         </is>
       </c>
       <c r="B50" s="16">
@@ -3549,7 +3588,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Formula bond equiv. yield. Default classico 2,0% sul prospetto, ma a prezzo 104 con 2y residui → YTM ~0% reale.</t>
+          <t>Formula bond equiv. yield. Cedola 2,0% sul prospetto, ma a prezzo 101,97 con 1,8y residui → YTM reale ~0,9%.</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Default classico 1,6% sul prospetto, a prezzo 102 con 4y residui → YTM ~1,1% reale.</t>
+          <t>Cedola 1,6% sul prospetto, a prezzo 101,92 con 4y residui → YTM reale ~1,1%.</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3620,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>YTM reale effettivo (media mag 2028 + giu 2030)</t>
+          <t>YTM reale effettivo (media mar 2028 + giu 2030)</t>
         </is>
       </c>
       <c r="B56" s="16">
@@ -3606,7 +3645,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>YTM reale NETTO mag 2028</t>
+          <t>YTM reale NETTO mar 2028</t>
         </is>
       </c>
       <c r="B59" s="16">
@@ -3636,24 +3675,160 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>BTP Valore / BTP Futura - PREZZI MOT (per YTM di chi compra oggi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo MOT BTP Valore mar 2026</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Anni residui</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Quotazione ufficiale MOT 09/06/2026: 98,65 (SOTTO la pari). Scadenza 10/03/2032. Il premio fedelta' 0,8% NON spetta a chi compra sul MOT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo MOT BTP Futura nov 2033</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Anni residui</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Quotazione ufficiale MOT 09/06/2026: 86,15 (forte sconto sotto par → YTM lordo ~3,65%). Scadenza 16/11/2033. Il doppio premio PIL NON spetta a chi compra sul MOT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Anagrafica ISIN (Borsa Italiana MOT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>BTP Italia mar 2028</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>IT0005532723</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Scadenza 14/03/2028 (il titolo e' MARZO 2028: la serie 'mag 2028' non esiste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>BTP Italia giu 2030</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>IT0005497000</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Scadenza 28/06/2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>BTP Valore mar 2026</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>IT0005696338</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>7a emissione, scadenza 10/03/2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>BTP Futura nov 2033</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>IT0005466351</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>4a emissione nov 2021, scadenza 16/11/2033</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3715,7 +3890,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>'1 - Parametri'!B6</f>
         <v/>
       </c>
@@ -3737,7 +3912,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -3748,7 +3923,7 @@
           <t>Capitale investito (EUR)</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -3761,27 +3936,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Infl. FOI media</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Cedola lorda annua</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Importo netto su cap.</t>
         </is>
@@ -3793,7 +3968,7 @@
           <t>1 - Disinflazione 1,0%</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
@@ -3805,7 +3980,7 @@
         <f>C13*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>$B$9*D13</f>
         <v/>
       </c>
@@ -3816,7 +3991,7 @@
           <t>2 - Base BCE 2,0%</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
@@ -3828,7 +4003,7 @@
         <f>C14*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>$B$9*D14</f>
         <v/>
       </c>
@@ -3839,7 +4014,7 @@
           <t>3 - Persistente 3,0%</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
@@ -3851,7 +4026,7 @@
         <f>C15*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>$B$9*D15</f>
         <v/>
       </c>
@@ -3862,7 +4037,7 @@
           <t>4 - Stress geopol. 4,5%</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
@@ -3874,7 +4049,7 @@
         <f>C16*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>$B$9*D16</f>
         <v/>
       </c>
@@ -3887,32 +4062,32 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Cedole nette tot 5y</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Premio netto fedelta'</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Tot. netto incassato</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>IRR nom netto annuo (lineare)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>IRR reale netto</t>
         </is>
@@ -3924,15 +4099,15 @@
           <t>1 - Disinflazione 1,0%</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <f>E13*$B$6</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>B20+C20</f>
         <v/>
       </c>
@@ -3951,15 +4126,15 @@
           <t>2 - Base BCE 2,0%</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>E14*$B$6</f>
         <v/>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>B21+C21</f>
         <v/>
       </c>
@@ -3978,15 +4153,15 @@
           <t>3 - Persistente 3,0%</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>E15*$B$6</f>
         <v/>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>B22+C22</f>
         <v/>
       </c>
@@ -4005,15 +4180,15 @@
           <t>4 - Stress geopol. 4,5%</t>
         </is>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <f>E16*$B$6</f>
         <v/>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>B23+C23</f>
         <v/>
       </c>
@@ -4131,7 +4306,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -4142,7 +4317,7 @@
           <t>Capitale investito (EUR)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -4155,27 +4330,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>FOI cumulata 5y</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Capitale rivalutato</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>Cedole nette 5y (su cap. rivalut.)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Tot. netto 5y (cedole + rivalut.)</t>
         </is>
@@ -4187,19 +4362,19 @@
           <t>1 - Disinflazione 1,0%</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>$B$8*(1+B12)^$B$6</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>$B$5*$B$8*((1+B12)^$B$6-1)/B12*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>(C12-$B$8)*(1-$B$7)+D12</f>
         <v/>
       </c>
@@ -4210,19 +4385,19 @@
           <t>2 - Base BCE 2,0%</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <f>$B$8*(1+B13)^$B$6</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>$B$5*$B$8*((1+B13)^$B$6-1)/B13*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>(C13-$B$8)*(1-$B$7)+D13</f>
         <v/>
       </c>
@@ -4233,19 +4408,19 @@
           <t>3 - Persistente 3,0%</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>$B$8*(1+B14)^$B$6</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>$B$5*$B$8*((1+B14)^$B$6-1)/B14*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>(C14-$B$8)*(1-$B$7)+D14</f>
         <v/>
       </c>
@@ -4256,19 +4431,19 @@
           <t>4 - Stress geopol. 4,5%</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>$B$8*(1+B15)^$B$6</f>
         <v/>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <f>$B$5*$B$8*((1+B15)^$B$6-1)/B15*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>(C15-$B$8)*(1-$B$7)+D15</f>
         <v/>
       </c>
@@ -4281,17 +4456,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Tot. netto 5y</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>IRR netto annuo</t>
         </is>
@@ -4303,7 +4478,7 @@
           <t>1 - Disinflazione 1,0%</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <f>E12</f>
         <v/>
       </c>
@@ -4318,7 +4493,7 @@
           <t>2 - Base BCE 2,0%</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <f>E13</f>
         <v/>
       </c>
@@ -4333,7 +4508,7 @@
           <t>3 - Persistente 3,0%</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>E14</f>
         <v/>
       </c>
@@ -4348,7 +4523,7 @@
           <t>4 - Stress geopol. 4,5%</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>E15</f>
         <v/>
       </c>
@@ -4416,7 +4591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4497,7 +4672,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <f>'1 - Parametri'!B19</f>
         <v/>
       </c>
@@ -4508,7 +4683,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -4519,7 +4694,7 @@
           <t>Capitale investito</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -4532,27 +4707,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Cedola lorda annua</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Importo netto x anno</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>Importo netto x fase (2y)</t>
         </is>
@@ -4568,15 +4743,15 @@
         <f>B5</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>B5*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <f>$B$11*C15</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>D15*2</f>
         <v/>
       </c>
@@ -4584,22 +4759,22 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Anni 3-4 (2,80%)</t>
+          <t>Anni 3-4 (3,20%)</t>
         </is>
       </c>
       <c r="B16" s="16">
         <f>B6</f>
         <v/>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>B6*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>$B$11*C16</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>D16*2</f>
         <v/>
       </c>
@@ -4614,15 +4789,15 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <f>B7*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <f>$B$11*C17</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>D17*2</f>
         <v/>
       </c>
@@ -4640,7 +4815,7 @@
           <t>Tot. cedole nette 6y</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <f>E15+E16+E17</f>
         <v/>
       </c>
@@ -4651,7 +4826,7 @@
           <t>Premio fedelta' netto</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>B11*B8*(1-B10)</f>
         <v/>
       </c>
@@ -4662,7 +4837,7 @@
           <t>Tot. netto 6y</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>B20+B21</f>
         <v/>
       </c>
@@ -4692,16 +4867,184 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Comprato OGGI sul MOT - YTM a prezzo 98,65 (sotto la pari)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo MOT (uff. 09/06/2026)</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>'1 - Parametri'!B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Anni residui (scad. 10/03/2032)</t>
+        </is>
+      </c>
+      <c r="B30" s="23">
+        <f>'1 - Parametri'!D64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Cedola media residua (step pesati sugli anni rimasti)</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>(B5*MAX(0,B30-4)+B6*MIN(2,MAX(0,B30-2))+B7*MIN(2,B30))/B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>YTM lordo (formula bond equivalent yield)</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>(B31*100+(100-B29)/B30)/((100+B29)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>YTM netto (tassazione 12,5%)</t>
+        </is>
+      </c>
+      <c r="B33" s="16">
+        <f>B32*(1-B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Comprato OGGI SOTTO la pari (98,65): il mercato sconta tassi saliti dopo il collocamento, quindi il YTM lordo (~3,48%) e' SUPERIORE alla media delle cedole (~3,23% sugli anni residui). ATTENZIONE: il premio fedelta' 0,8% NON spetta a chi compra sul MOT (solo sottoscrittori in collocamento), percio' il YTM qui sopra NON lo include.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>IRR reale netto per scenario (da YTM MOT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Scenario inflazione</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Infl. FOI media</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>IRR reale netto (YTM netto - FOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>1 - Disinflazione 1,0%</t>
+        </is>
+      </c>
+      <c r="B38" s="19">
+        <f>'1 - Parametri'!B37</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>$B$33-B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>2 - Base BCE 2,0%</t>
+        </is>
+      </c>
+      <c r="B39" s="19">
+        <f>'1 - Parametri'!B38</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>$B$33-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>3 - Persistente 3,0%</t>
+        </is>
+      </c>
+      <c r="B40" s="19">
+        <f>'1 - Parametri'!B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>$B$33-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>4 - Stress geopol. 4,5%</t>
+        </is>
+      </c>
+      <c r="B41" s="19">
+        <f>'1 - Parametri'!B40</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>$B$33-B41</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
+  <conditionalFormatting sqref="C38:C41">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F87171"/>
+        <color rgb="00FEF3C7"/>
+        <color rgb="0086EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -4713,7 +5056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4759,7 +5102,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Cedola anni 5-7</t>
+          <t>Cedola anni 5-8</t>
         </is>
       </c>
       <c r="B6" s="16">
@@ -4770,7 +5113,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Cedola anni 8-12</t>
+          <t>Cedola anni 9-12</t>
         </is>
       </c>
       <c r="B7" s="16">
@@ -4806,7 +5149,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>'1 - Parametri'!B27</f>
         <v/>
       </c>
@@ -4817,7 +5160,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -4828,7 +5171,7 @@
           <t>Capitale</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -4841,32 +5184,32 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Scenario PIL nominale medio</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>PIL nom. medio</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>Premio fed. atteso</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Cedole nette 12y</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>Tot. netto 12y</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>IRR nom netto annuo (lineare)</t>
         </is>
@@ -4885,11 +5228,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B16))</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>D16+$B$12*C16*(1-$B$11)</f>
         <v/>
       </c>
@@ -4911,11 +5254,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B17))</f>
         <v/>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>D17+$B$12*C17*(1-$B$11)</f>
         <v/>
       </c>
@@ -4937,11 +5280,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B18))</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>D18+$B$12*C18*(1-$B$11)</f>
         <v/>
       </c>
@@ -4953,28 +5296,196 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NOTA: BTP Futura NON e' piu' emesso dal 2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t>NOTA: BTP Futura NON e' piu' emesso dal 2021 (ricostruzione storica = contesto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Sul secondario disponibili 4 ISIN ma cedole molto basse (0,35-1,0%). Confronto utile per capire la LOGICA del premio fedelta', non per acquisto attuale. Struttura step-up 4+4+4 anni (1-4: 0,35%, 5-8: 0,60%, 9-12: 1,00%).</t>
-        </is>
+          <t>La tabella sopra RICOSTRUISCE il collocamento nov 2021 (chi sottoscrisse a 100 con premio PIL). Struttura step-up 4+4+4 anni DEFINITIVA 4a emissione (1-4: 0,75%, 5-8: 1,35%, 9-12: 1,70%). Per chi compra OGGI vale la sezione qui sotto: prezzo MOT 86,15 e NIENTE premio PIL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Comprato OGGI sul MOT - prezzo 86,15 → YTM lordo ~3,65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo MOT (uff. 09/06/2026)</t>
+        </is>
+      </c>
+      <c r="B24" s="23">
+        <f>'1 - Parametri'!B66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Anni residui (scad. 16/11/2033)</t>
+        </is>
+      </c>
+      <c r="B25" s="23">
+        <f>'1 - Parametri'!D66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Cedola media residua (step pesati sugli anni rimasti)</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>(B5*MAX(0,B25-8)+B6*MIN(4,MAX(0,B25-4))+B7*MIN(4,B25))/B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>YTM lordo (formula bond equivalent yield)</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>(B26*100+(100-B24)/B25)/((100+B24)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>YTM netto (tassazione 12,5%)</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>B27*(1-B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Il forte sconto sotto par (86,15) compensa le cedole basse: quasi tutto il rendimento arriva dal capital gain a scadenza (100-86,15 su 7,4 anni). ATTENZIONE: il doppio premio PIL spetta SOLO ai sottoscrittori originali del nov 2021, NON a chi compra sul MOT — il YTM qui sopra correttamente lo esclude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>IRR reale netto per scenario (da YTM MOT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Scenario inflazione</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Infl. FOI media</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>IRR reale netto (YTM netto - FOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>1 - Disinflazione 1,0%</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>'1 - Parametri'!B37</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>$B$28-B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2 - Base BCE 2,0%</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>'1 - Parametri'!B38</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>$B$28-B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>3 - Persistente 3,0%</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>'1 - Parametri'!B39</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>$B$28-B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>4 - Stress geopol. 4,5%</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>'1 - Parametri'!B40</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>$B$28-B36</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
+  <conditionalFormatting sqref="C33:C36">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F87171"/>
+        <color rgb="00FEF3C7"/>
+        <color rgb="0086EFAC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E16:E18">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5028,27 +5539,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Scadenza</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Rendimento lordo</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Tot. cedole nette a scad.</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Cedola netta annua EUR</t>
         </is>
@@ -5060,7 +5571,7 @@
           <t>Tassazione 12,5% applicata</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -5071,13 +5582,13 @@
           <t>Capitale (default Parametri)</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Rendim. lordo (curva)</t>
         </is>
@@ -5093,15 +5604,15 @@
         <f>'1 - Parametri'!B30</f>
         <v/>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>B9*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>$B$7*C9*2</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>$B$7*C9</f>
         <v/>
       </c>
@@ -5116,15 +5627,15 @@
         <f>'1 - Parametri'!B31</f>
         <v/>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="22">
         <f>B10*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>$B$7*C10*3</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>$B$7*C10</f>
         <v/>
       </c>
@@ -5139,15 +5650,15 @@
         <f>'1 - Parametri'!B32</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>B11*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>$B$7*C11*5</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>$B$7*C11</f>
         <v/>
       </c>
@@ -5162,15 +5673,15 @@
         <f>'1 - Parametri'!B33</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="22">
         <f>B12*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>$B$7*C12*7</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>$B$7*C12</f>
         <v/>
       </c>
@@ -5185,15 +5696,15 @@
         <f>'1 - Parametri'!B34</f>
         <v/>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>B13*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>$B$7*C13*10</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>$B$7*C13</f>
         <v/>
       </c>
@@ -5231,7 +5742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5244,7 +5755,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MATRICE: rendimento REALE netto annuo - 5 strumenti x 4 scenari</t>
+          <t>MATRICE: rendimento REALE netto annuo - 6 strumenti x 4 scenari</t>
         </is>
       </c>
     </row>
@@ -5263,27 +5774,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Strumento</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Infl. 1,0%</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Infl. 2,0%</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Infl. 3,0%</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Infl. 4,5%</t>
         </is>
@@ -5338,95 +5849,118 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>BTP Valore (avg 3,07% lordo)</t>
+          <t>BTP Valore (YTM lordo MOT ~3,48%)</t>
         </is>
       </c>
       <c r="B8" s="16">
-        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
+        <f>'4 - BTP Valore'!$B$32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
+        <f>'4 - BTP Valore'!$B$32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
+        <f>'4 - BTP Valore'!$B$32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>((2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
+        <f>'4 - BTP Valore'!$B$32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>BTP nominale 5y (2,90% lordo)</t>
+          <t>BTP Futura (YTM lordo MOT ~3,65%)</t>
         </is>
       </c>
       <c r="B9" s="16">
-        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
+        <f>'5 - BTP Futura'!$B$27*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
+        <f>'5 - BTP Futura'!$B$27*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
+        <f>'5 - BTP Futura'!$B$27*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
+        <f>'5 - BTP Futura'!$B$27*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>BTP nominale 5y (2,90% lordo)</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>BTP nominale 10y (3,45% lordo)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B11" s="16">
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C11" s="16">
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D11" s="16">
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E11" s="16">
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Heatmap: VERDE = miglior rendimento REALE per scenario / ROSSO = peggior</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>BTP Italia Si vince in scenari di inflazione media-alta perche' il tasso fisso e' REALE. BTP Italia classico in inflazione alta ha vantaggio capitale rivalutato. Nominali: vincono solo in disinflazione.</t>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>BTP Italia Si vince in scenari di inflazione media-alta perche' il tasso fisso e' REALE. BTP Italia classico in inflazione alta ha vantaggio capitale rivalutato. Valore e Futura: YTM da prezzo MOT (comprati OGGI, senza premi fedelta'/PIL), cedola nominale fissa → vincono solo con inflazione bassa. Nominali: vincono solo in disinflazione.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:B10">
+  <conditionalFormatting sqref="B6:B11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5438,7 +5972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C10">
+  <conditionalFormatting sqref="C6:C11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5450,7 +5984,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D10">
+  <conditionalFormatting sqref="D6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5462,7 +5996,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E6:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5517,27 +6051,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Avversario</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Rendimento lordo</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Rend. netto (1-12,5%)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Soglia infl. break-even (lorda)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Verdetto</t>
         </is>
@@ -5561,7 +6095,7 @@
         <f>B6-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="24">
         <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D6*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5584,7 +6118,7 @@
         <f>B7-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="24">
         <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D7*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5607,7 +6141,7 @@
         <f>B8-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="24">
         <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D8*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5630,7 +6164,7 @@
         <f>B9-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="24">
         <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D9*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5653,7 +6187,7 @@
         <f>B10-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D10*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5661,11 +6195,11 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>BTP Valore (avg+premio)</t>
+          <t>BTP Valore (YTM lordo MOT 98,65)</t>
         </is>
       </c>
       <c r="B11" s="16">
-        <f>(2*'1 - Parametri'!B15+2*'1 - Parametri'!B16+2*'1 - Parametri'!B17)/6+('1 - Parametri'!B18)/6</f>
+        <f>'4 - BTP Valore'!B32</f>
         <v/>
       </c>
       <c r="C11" s="16">
@@ -5676,7 +6210,7 @@
         <f>B11-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="24">
         <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D11*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5684,11 +6218,11 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>BTP Futura (avg cedole+premio PIL 3%)</t>
+          <t>BTP Futura (YTM lordo MOT 86,15)</t>
         </is>
       </c>
       <c r="B12" s="16">
-        <f>(4*'1 - Parametri'!B22+4*'1 - Parametri'!B23+4*'1 - Parametri'!B24)/12+MAX('1 - Parametri'!B25,MIN('1 - Parametri'!B26,0.4*0.03))/12</f>
+        <f>'5 - BTP Futura'!B27</f>
         <v/>
       </c>
       <c r="C12" s="16">
@@ -5699,7 +6233,7 @@
         <f>B12-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="24">
         <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D12*100,2)&amp;"%"))</f>
         <v/>
       </c>
@@ -5712,27 +6246,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Avversario</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>YTM reale NETTO (MOT)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>Sì reale netto</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Vantaggio Sì (pp)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>Verdetto</t>
         </is>
@@ -5756,7 +6290,7 @@
         <f>C16-B16</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="24">
         <f>IF(D16&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D16*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D16*100,2)&amp;"pp)")</f>
         <v/>
       </c>
@@ -5779,7 +6313,7 @@
         <f>C17-B17</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="24">
         <f>IF(D17&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D17*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D17*100,2)&amp;"pp)")</f>
         <v/>
       </c>
@@ -5802,7 +6336,7 @@
         <f>C18-B18</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="24">
         <f>IF(D18&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D18*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D18*100,2)&amp;"pp)")</f>
         <v/>
       </c>
@@ -5810,14 +6344,14 @@
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ATTENZIONE: usato YTM REALE EFFETTIVO calcolato dal prezzo MOT (non cedola del prospetto). Se sul secondario il classico quota SOPRA par (es. 104), il YTM reale si abbassa molto, specie per scadenze brevi. Esempio default: mag 2028 a 104, YTM reale ~0% (premio erode tutto). Vai al foglio Parametri righe 46-56 per modificare i prezzi MOT e vedere come cambia.</t>
+          <t>ATTENZIONE: usato YTM REALE EFFETTIVO calcolato dal prezzo MOT (non cedola del prospetto). Se sul secondario il classico quota SOPRA par, il YTM reale si abbassa, specie per scadenze brevi. Esempio coi prezzi uff. 09/06/2026: mar 2028 a 101,97 → YTM reale ~0,9%; giu 2030 a 101,92 → ~1,1%. Vai al foglio Parametri righe 46-56 per modificare i prezzi MOT.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>BTP Futura: cedole FISSE step-up molto basse (0,35%/0,60%/1,00%) + premio PIL nominale (0,4-3% diluito su 12y). Rendimento totale annuo molto inferiore al Sì → Sì vince SEMPRE indipendentemente dall'inflazione. Sospeso dal 2021, solo secondario.</t>
+          <t>BTP Futura comprato OGGI sul MOT a 86,15 (forte sconto sotto par): YTM lordo ~3,65% nonostante le cedole step-up basse (0,75/1,35/1,70). Soglia break-even FOI ~2,3%: sotto, il Futura vince; sopra, vince il Sì. Il doppio premio PIL NON spetta a chi compra sul MOT (solo sottoscrittori originali nov 2021).</t>
         </is>
       </c>
     </row>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -3137,7 +3137,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BTP Italia mar 2028 - cedola reale annua</t>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>MEF IT0005532723, scadenza 14/03/2028: tasso reale 2,0% sul prospetto (rendimento per chi compra a 100). NB: il titolo e' MARZO 2028, la serie 'mag 2028' non esiste.</t>
+          <t>MEF IT0005532723, scadenza 14/03/2028: tasso reale 2,0% sul prospetto (rendimento per chi compra a 100).</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
+    <row r="70" ht="15" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
           <t>BTP Italia mar 2028</t>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Scadenza 14/03/2028 (il titolo e' MARZO 2028: la serie 'mag 2028' non esiste)</t>
+          <t>Scadenza 14/03/2028</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>BTP Italia classico mag 2028 (YTM REALE da prezzo MOT)</t>
+          <t>BTP Italia classico mar 2028 (YTM REALE da prezzo MOT)</t>
         </is>
       </c>
       <c r="B16" s="16">

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -2348,10 +2348,9 @@
           <t>3 - BTP Italia classico</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Capitale rivalutato + cedola reale 1,6% (giu 2030)</t>
-        </is>
+      <c r="B7" s="5">
+        <f>"Capitale rivalutato + cedola reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B12*100,1)&amp;"",".",",")&amp;"% (giu 2030)"</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2360,10 +2359,9 @@
           <t>4 - BTP Valore</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Step-up 2,60/3,20/3,80 + YTM a prezzo MOT 98,65</t>
-        </is>
+      <c r="B8" s="5">
+        <f>"Step-up "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B15*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B16*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B17*100,2)&amp;"",".",",")&amp;" + YTM a prezzo MOT "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B64,2)&amp;"",".",",")</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2372,10 +2370,9 @@
           <t>5 - BTP Futura</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Storico 4a emissione + YTM a prezzo MOT 86,15</t>
-        </is>
+      <c r="B9" s="5">
+        <f>"Storico 4a emissione + YTM a prezzo MOT "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B66,2)&amp;"",".",",")</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2488,31 +2485,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>• MEF - BTP Italia marzo 2028 (IT0005532723, scad. 14/03/2028) tasso reale 2,0%; giugno 2030 (IT0005497000) tasso reale 1,6%</t>
-        </is>
+      <c r="A24" s="5">
+        <f>"• MEF - BTP Italia marzo 2028 (IT0005532723, scad. 14/03/2028) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B11*100,1)&amp;"",".",",")&amp;"%; giugno 2030 (IT0005497000) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B12*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>• MEF - BTP Valore marzo 2026 (IT0005696338) step-up DEFINITIVI 2,60/3,20/3,80% + premio 0,8%, scadenza 10 mar 2032</t>
-        </is>
+      <c r="A25" s="5">
+        <f>"• MEF - BTP Valore marzo 2026 (IT0005696338) step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B15*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B16*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B17*100,2)&amp;"",".",",")&amp;"% + premio "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B18*100,1)&amp;"",".",",")&amp;"%, scadenza 10 mar 2032"</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>• MEF - BTP Futura 4a emissione nov 2021 (IT0005466351), 12 anni step-up DEFINITIVI 0,75/1,35/1,70% + doppio premio PIL (solo sottoscrittori originali), scadenza 16 nov 2033</t>
-        </is>
+      <c r="A26" s="5">
+        <f>"• MEF - BTP Futura 4a emissione nov 2021 (IT0005466351), "&amp;'1 - Parametri'!B27&amp;" anni step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B22*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B23*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B24*100,2)&amp;"",".",",")&amp;"% + doppio premio PIL (solo sottoscrittori originali), scadenza 16 nov 2033"</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>• Borsa Italiana MOT - prezzi ufficiali 09/06/2026: mar 2028 101,97; giu 2030 101,92; Valore 98,65; Futura 86,15</t>
-        </is>
+      <c r="A27" s="5">
+        <f>"• Borsa Italiana MOT - prezzi ufficiali correnti (foglio 1 - Parametri): mar 2028 "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B46,2)&amp;"",".",",")&amp;"; giu 2030 "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B48,2)&amp;"",".",",")&amp;"; Valore "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B64,2)&amp;"",".",",")&amp;"; Futura "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B66,2)&amp;"",".",",")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -2893,7 +2886,7 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
         <v/>
       </c>
       <c r="C12" s="24">
@@ -3094,13 +3087,12 @@
       <c r="B6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Fissa: 5 anni</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+      <c r="D6" s="10">
+        <f>"Fissa: "&amp;B6&amp;" anni"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta' finale</t>
@@ -3109,13 +3101,12 @@
       <c r="B7" s="9" t="n">
         <v>0.006</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Confermato MEF: 0,6% del capitale (solo se mantenuto a scadenza)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="D7" s="10">
+        <f>"Confermato MEF: "&amp;SUBSTITUTE(ROUND(B7*100,1)&amp;"",".",",")&amp;"% del capitale (solo se mantenuto a scadenza)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Tassazione titoli di stato</t>
@@ -3124,10 +3115,9 @@
       <c r="B8" s="12" t="n">
         <v>0.125</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>12,5% su cedole + premio finale</t>
-        </is>
+      <c r="D8" s="10">
+        <f>"Aliquota "&amp;SUBSTITUTE(ROUND(B8*100,1)&amp;"",".",",")&amp;"% su cedole + premio finale"</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3137,7 +3127,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>BTP Italia mar 2028 - cedola reale annua</t>
@@ -3146,13 +3136,12 @@
       <c r="B11" s="9" t="n">
         <v>0.02</v>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>MEF IT0005532723, scadenza 14/03/2028: tasso reale 2,0% sul prospetto (rendimento per chi compra a 100).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="D11" s="10">
+        <f>"MEF IT0005532723, scadenza 14/03/2028: tasso reale "&amp;SUBSTITUTE(ROUND(B11*100,1)&amp;"",".",",")&amp;"% sul prospetto (rendimento per chi compra a 100)."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BTP Italia giu 2030 - cedola reale annua</t>
@@ -3161,10 +3150,9 @@
       <c r="B12" s="9" t="n">
         <v>0.016</v>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>MEF IT0005497000, scadenza 28/06/2030: tasso reale 1,6% sul prospetto</t>
-        </is>
+      <c r="D12" s="10">
+        <f>"MEF IT0005497000, scadenza 28/06/2030: tasso reale "&amp;SUBSTITUTE(ROUND(B12*100,1)&amp;"",".",",")&amp;"% sul prospetto"</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3174,7 +3162,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 1-2</t>
@@ -3183,13 +3171,12 @@
       <c r="B15" s="9" t="n">
         <v>0.026</v>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>MEF: 2,60% definitivo (cedole trimestrali)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="D15" s="10">
+        <f>"MEF: "&amp;SUBSTITUTE(ROUND(B15*100,2)&amp;"",".",",")&amp;"% definitivo (cedole trimestrali)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 3-4</t>
@@ -3198,13 +3185,12 @@
       <c r="B16" s="9" t="n">
         <v>0.032</v>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>MEF: 3,20% definitivo (il 2,80 era il minimo garantito pre-collocamento)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="D16" s="10">
+        <f>"MEF: "&amp;SUBSTITUTE(ROUND(B16*100,2)&amp;"",".",",")&amp;"% definitivo (il 2,80 era il minimo garantito pre-collocamento)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 5-6</t>
@@ -3213,13 +3199,12 @@
       <c r="B17" s="9" t="n">
         <v>0.038</v>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>MEF: 3,80% (definitivo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="D17" s="10">
+        <f>"MEF: "&amp;SUBSTITUTE(ROUND(B17*100,2)&amp;"",".",",")&amp;"% (definitivo)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta'</t>
@@ -3228,10 +3213,9 @@
       <c r="B18" s="9" t="n">
         <v>0.008</v>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>MEF: 0,8% del capitale a scadenza (solo sottoscrittori in collocamento)</t>
-        </is>
+      <c r="D18" s="10">
+        <f>"MEF: "&amp;SUBSTITUTE(ROUND(B18*100,1)&amp;"",".",",")&amp;"% del capitale a scadenza (solo sottoscrittori in collocamento)"</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -3256,7 +3240,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 1-4</t>
@@ -3265,13 +3249,12 @@
       <c r="B22" s="9" t="n">
         <v>0.0075</v>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>MEF 4a emissione nov 2021, step DEFINITIVI: 0,75% (NON 0,35 = 2a emissione)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+      <c r="D22" s="10">
+        <f>"MEF 4a emissione nov 2021, step DEFINITIVI: "&amp;SUBSTITUTE(ROUND(B22*100,2)&amp;"",".",",")&amp;"% (NON 0,35 = 2a emissione)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 5-8</t>
@@ -3280,13 +3263,12 @@
       <c r="B23" s="9" t="n">
         <v>0.0135</v>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>MEF definitivo: 1,35% (anni 5-8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+      <c r="D23" s="10">
+        <f>"MEF definitivo: "&amp;SUBSTITUTE(ROUND(B23*100,2)&amp;"",".",",")&amp;"% (anni 5-8)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Cedola step-up anni 9-12</t>
@@ -3295,13 +3277,12 @@
       <c r="B24" s="9" t="n">
         <v>0.017</v>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>MEF definitivo: 1,70% (anni 9-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+      <c r="D24" s="10">
+        <f>"MEF definitivo: "&amp;SUBSTITUTE(ROUND(B24*100,2)&amp;"",".",",")&amp;"% (anni 9-12)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta' min (PIL)</t>
@@ -3310,13 +3291,12 @@
       <c r="B25" s="9" t="n">
         <v>0.004</v>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Floor 0,4% se PIL nominale basso (solo sottoscrittori originali)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+      <c r="D25" s="10">
+        <f>"Floor "&amp;SUBSTITUTE(ROUND(B25*100,1)&amp;"",".",",")&amp;"% se PIL nominale basso (solo sottoscrittori originali)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Premio fedelta' max (PIL)</t>
@@ -3325,10 +3305,9 @@
       <c r="B26" s="9" t="n">
         <v>0.03</v>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Cap 3,0% se PIL nominale alto (solo sottoscrittori originali)</t>
-        </is>
+      <c r="D26" s="10">
+        <f>"Cap "&amp;SUBSTITUTE(ROUND(B26*100,1)&amp;"",".",",")&amp;"% se PIL nominale alto (solo sottoscrittori originali)"</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -3353,7 +3332,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>BTP 2y - rendimento lordo (feb 2028)</t>
@@ -3362,13 +3341,12 @@
       <c r="B30" s="9" t="n">
         <v>0.022</v>
       </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>MEF asta: 2,20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+      <c r="D30" s="10">
+        <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B30*100,2)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>BTP 3y - rendimento lordo (mar 2029)</t>
@@ -3377,10 +3355,9 @@
       <c r="B31" s="9" t="n">
         <v>0.024</v>
       </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>MEF asta: 2,40%</t>
-        </is>
+      <c r="D31" s="10">
+        <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B31*100,2)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -3398,7 +3375,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>BTP 7y - rendimento lordo (mar 2033)</t>
@@ -3407,13 +3384,12 @@
       <c r="B33" s="9" t="n">
         <v>0.0315</v>
       </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>MEF asta: 3,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+      <c r="D33" s="10">
+        <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B33*100,2)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>BTP 10y - rendimento lordo (feb 2036)</t>
@@ -3422,20 +3398,18 @@
       <c r="B34" s="9" t="n">
         <v>0.0345</v>
       </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>MEF asta: 3,45%</t>
-        </is>
+      <c r="D34" s="10">
+        <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B34*100,2)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Scenari inflazione FOI media 5 anni (per simulazioni)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+      <c r="A36" s="7">
+        <f>"Scenari inflazione FOI media "&amp;B6&amp;" anni (per simulazioni)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Scenario 1: Disinflazione</t>
@@ -3444,13 +3418,12 @@
       <c r="B37" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>BCE stretta riuscita - inflazione 1,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+      <c r="D37" s="10">
+        <f>"BCE stretta riuscita - inflazione "&amp;SUBSTITUTE(ROUND(B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Scenario 2: Base BCE</t>
@@ -3459,13 +3432,12 @@
       <c r="B38" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Target 2,0% medio termine</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+      <c r="D38" s="10">
+        <f>"Target "&amp;SUBSTITUTE(ROUND(B38*100,1)&amp;"",".",",")&amp;"% medio termine"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Scenario 3: Persistente</t>
@@ -3474,13 +3446,12 @@
       <c r="B39" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Inflazione struturale 3,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+      <c r="D39" s="10">
+        <f>"Inflazione strutturale "&amp;SUBSTITUTE(ROUND(B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Scenario 4: Stress geopol.</t>
@@ -3489,10 +3460,9 @@
       <c r="B40" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Brent 120 USD persistente - 4,5%</t>
-        </is>
+      <c r="D40" s="10">
+        <f>"Brent 120 USD persistente - "&amp;SUBSTITUTE(ROUND(B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3542,11 +3512,10 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Quotazione ufficiale MOT 09/06/2026: 101,97 (100 = par). Aggiorna col valore corrente quando cambia il mercato.</t>
-        </is>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="10">
+        <f>"Quotazione ufficiale MOT corrente: "&amp;SUBSTITUTE(ROUND(B46,2)&amp;"",".",",")&amp;" (100 = par). Aggiorna col valore corrente quando cambia il mercato."</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3567,11 +3536,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Quotazione ufficiale MOT 09/06/2026: 101,92. Aggiorna col valore corrente quando cambia il mercato.</t>
-        </is>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="10">
+        <f>"Quotazione ufficiale MOT corrente: "&amp;SUBSTITUTE(ROUND(B48,2)&amp;"",".",",")&amp;". Aggiorna col valore corrente quando cambia il mercato."</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3585,11 +3553,10 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Formula bond equiv. yield. Cedola 2,0% sul prospetto, ma a prezzo 101,97 con 1,8y residui → YTM reale ~0,9%.</t>
-        </is>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="10">
+        <f>"Formula bond equiv. yield. Cedola "&amp;SUBSTITUTE(ROUND(B11*100,1)&amp;"",".",",")&amp;"% sul prospetto, ma a prezzo "&amp;SUBSTITUTE(ROUND(B46,2)&amp;"",".",",")&amp;" con "&amp;SUBSTITUTE(ROUND(D46,1)&amp;"",".",",")&amp;"y residui → YTM reale ~"&amp;SUBSTITUTE(ROUND(B50*100,2)&amp;"",".",",")&amp;"%."</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -3603,11 +3570,10 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Cedola 1,6% sul prospetto, a prezzo 101,92 con 4y residui → YTM reale ~1,1%.</t>
-        </is>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="10">
+        <f>"Cedola "&amp;SUBSTITUTE(ROUND(B12*100,1)&amp;"",".",",")&amp;"% sul prospetto, a prezzo "&amp;SUBSTITUTE(ROUND(B48,2)&amp;"",".",",")&amp;" con "&amp;SUBSTITUTE(ROUND(D48,1)&amp;"",".",",")&amp;"y residui → YTM reale ~"&amp;SUBSTITUTE(ROUND(B52*100,2)&amp;"",".",",")&amp;"%."</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -3700,11 +3666,10 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Quotazione ufficiale MOT 09/06/2026: 98,65 (SOTTO la pari). Scadenza 10/03/2032. Il premio fedelta' 0,8% NON spetta a chi compra sul MOT.</t>
-        </is>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="10">
+        <f>"Quotazione ufficiale MOT corrente: "&amp;SUBSTITUTE(ROUND(B64,2)&amp;"",".",",")&amp;IF(B64&lt;100," (SOTTO la pari)",IF(B64&gt;100," (sopra la pari)"," (alla pari)"))&amp;". Scadenza 10/03/2032. Il premio fedelta' "&amp;SUBSTITUTE(ROUND(B18*100,1)&amp;"",".",",")&amp;"% NON spetta a chi compra sul MOT."</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -3726,10 +3691,9 @@
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Quotazione ufficiale MOT 09/06/2026: 86,15 (forte sconto sotto par → YTM lordo ~3,65%). Scadenza 16/11/2033. Il doppio premio PIL NON spetta a chi compra sul MOT.</t>
-        </is>
+      <c r="A67" s="10">
+        <f>"Quotazione ufficiale MOT corrente: "&amp;SUBSTITUTE(ROUND(B66,2)&amp;"",".",",")&amp;" → YTM lordo ~"&amp;SUBSTITUTE(ROUND('5 - BTP Futura'!B27*100,2)&amp;"",".",",")&amp;"%. Scadenza 16/11/2033. Il doppio premio PIL NON spetta a chi compra sul MOT."</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -3963,10 +3927,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A13" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B13" s="19">
         <f>'1 - Parametri'!B37</f>
@@ -3986,10 +3949,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A14" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B14" s="19">
         <f>'1 - Parametri'!B38</f>
@@ -4009,10 +3971,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A15" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B15" s="19">
         <f>'1 - Parametri'!B39</f>
@@ -4032,10 +3993,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A16" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B16" s="19">
         <f>'1 - Parametri'!B40</f>
@@ -4055,10 +4015,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Rendimento totale finale 5 anni (netto, con premio 0,6%)</t>
-        </is>
+      <c r="A18" s="7">
+        <f>"Rendimento totale finale "&amp;'1 - Parametri'!B6&amp;" anni (netto, con premio "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B7*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -4067,10 +4026,9 @@
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>Cedole nette tot 5y</t>
-        </is>
+      <c r="B19" s="21">
+        <f>"Cedole nette tot "&amp;$B$6&amp;"y"</f>
+        <v/>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
@@ -4094,10 +4052,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A20" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B20" s="20">
         <f>E13*$B$6</f>
@@ -4121,10 +4078,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A21" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B21" s="20">
         <f>E14*$B$6</f>
@@ -4148,10 +4104,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A22" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B22" s="20">
         <f>E15*$B$6</f>
@@ -4175,10 +4130,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A23" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B23" s="20">
         <f>E16*$B$6</f>
@@ -4335,32 +4289,28 @@
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>FOI cumulata 5y</t>
-        </is>
+      <c r="B11" s="21">
+        <f>"FOI cumulata "&amp;$B$6&amp;"y"</f>
+        <v/>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Capitale rivalutato</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>Cedole nette 5y (su cap. rivalut.)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>Tot. netto 5y (cedole + rivalut.)</t>
-        </is>
+      <c r="D11" s="21">
+        <f>"Cedole nette "&amp;$B$6&amp;"y (su cap. rivalut.)"</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>"Tot. netto "&amp;$B$6&amp;"y (cedole + rivalut.)"</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A12" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B12" s="19">
         <f>'1 - Parametri'!B37</f>
@@ -4380,10 +4330,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A13" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B13" s="19">
         <f>'1 - Parametri'!B38</f>
@@ -4403,10 +4352,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A14" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B14" s="19">
         <f>'1 - Parametri'!B39</f>
@@ -4426,10 +4374,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A15" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B15" s="19">
         <f>'1 - Parametri'!B40</f>
@@ -4461,10 +4408,9 @@
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Tot. netto 5y</t>
-        </is>
+      <c r="B18" s="21">
+        <f>"Tot. netto "&amp;$B$6&amp;"y"</f>
+        <v/>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
@@ -4473,10 +4419,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A19" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B19" s="20">
         <f>E12</f>
@@ -4488,10 +4433,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A20" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B20" s="20">
         <f>E13</f>
@@ -4503,10 +4447,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A21" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B21" s="20">
         <f>E14</f>
@@ -4518,10 +4461,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A22" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B22" s="20">
         <f>E15</f>
@@ -4539,10 +4481,10 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Classico: l'inflazione cresce IL CAPITALE (effetto compounding). Si: l'inflazione cresce SOLO la cedola annua. Trade-off: il classico costa di piu' sul secondario (no premio se compri usato).</t>
+          <t>Classico: l'inflazione cresce IL CAPITALE (effetto compounding). Si: l'inflazione cresce SOLO la cedola annua. Trade-off: sul secondario il classico si paga al prezzo MOT corrente (vedi foglio Parametri) e chi compra usato NON ha il premio fedelta'.</t>
         </is>
       </c>
     </row>
@@ -4734,10 +4676,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Anni 1-2 (2,60%)</t>
-        </is>
+      <c r="A15" s="8">
+        <f>"Anni 1-2 ("&amp;SUBSTITUTE(ROUND(B5*100,2)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B15" s="16">
         <f>B5</f>
@@ -4757,10 +4698,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Anni 3-4 (3,20%)</t>
-        </is>
+      <c r="A16" s="8">
+        <f>"Anni 3-4 ("&amp;SUBSTITUTE(ROUND(B6*100,2)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B16" s="16">
         <f>B6</f>
@@ -4780,10 +4720,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Anni 5-6 (3,80%)</t>
-        </is>
+      <c r="A17" s="8">
+        <f>"Anni 5-6 ("&amp;SUBSTITUTE(ROUND(B7*100,2)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B17" s="16">
         <f>B7</f>
@@ -4803,17 +4742,15 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Rendimento totale netto 6 anni</t>
-        </is>
+      <c r="A19" s="7">
+        <f>"Rendimento totale netto "&amp;B9&amp;" anni"</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Tot. cedole nette 6y</t>
-        </is>
+      <c r="A20" s="8">
+        <f>"Tot. cedole nette "&amp;B9&amp;"y"</f>
+        <v/>
       </c>
       <c r="B20" s="20">
         <f>E15+E16+E17</f>
@@ -4832,10 +4769,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Tot. netto 6y</t>
-        </is>
+      <c r="A22" s="8">
+        <f>"Tot. netto "&amp;B9&amp;"y"</f>
+        <v/>
       </c>
       <c r="B22" s="20">
         <f>B20+B21</f>
@@ -4868,16 +4804,15 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Comprato OGGI sul MOT - YTM a prezzo 98,65 (sotto la pari)</t>
-        </is>
+      <c r="A28" s="7">
+        <f>"Comprato OGGI sul MOT - YTM a prezzo "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B64,2)&amp;"",".",",")&amp;IF('1 - Parametri'!B64&lt;100," (sotto la pari)",IF('1 - Parametri'!B64&gt;100," (sopra la pari)"," (alla pari)"))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Prezzo MOT (uff. 09/06/2026)</t>
+          <t>Prezzo MOT corrente (vedi foglio Parametri)</t>
         </is>
       </c>
       <c r="B29" s="23">
@@ -4919,21 +4854,19 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>YTM netto (tassazione 12,5%)</t>
-        </is>
+      <c r="A33" s="8">
+        <f>"YTM netto (tassazione "&amp;SUBSTITUTE(ROUND(B10*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B33" s="16">
         <f>B32*(1-B10)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Comprato OGGI SOTTO la pari (98,65): il mercato sconta tassi saliti dopo il collocamento, quindi il YTM lordo (~3,48%) e' SUPERIORE alla media delle cedole (~3,23% sugli anni residui). ATTENZIONE: il premio fedelta' 0,8% NON spetta a chi compra sul MOT (solo sottoscrittori in collocamento), percio' il YTM qui sopra NON lo include.</t>
-        </is>
+    <row r="34" ht="75" customHeight="1">
+      <c r="A34" s="10">
+        <f>"Prezzo MOT corrente "&amp;SUBSTITUTE(ROUND(B29,2)&amp;"",".",",")&amp;": YTM lordo ~"&amp;SUBSTITUTE(ROUND(B32*100,2)&amp;"",".",",")&amp;"% vs media cedole residue ~"&amp;SUBSTITUTE(ROUND(B31*100,2)&amp;"",".",",")&amp;"%. Se il prezzo e' sotto la pari il YTM supera la media cedole (sconto), se sopra la riduce. ATTENZIONE: il premio fedelta' "&amp;SUBSTITUTE(ROUND(B8*100,1)&amp;"",".",",")&amp;"% NON spetta a chi compra sul MOT (solo sottoscrittori in collocamento), percio' il YTM qui sopra NON lo include."</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4961,10 +4894,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A38" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B38" s="19">
         <f>'1 - Parametri'!B37</f>
@@ -4976,10 +4908,9 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A39" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B39" s="19">
         <f>'1 - Parametri'!B38</f>
@@ -4991,10 +4922,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A40" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B40" s="19">
         <f>'1 - Parametri'!B39</f>
@@ -5006,10 +4936,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A41" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B41" s="19">
         <f>'1 - Parametri'!B40</f>
@@ -5199,15 +5128,13 @@
           <t>Premio fed. atteso</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Cedole nette 12y</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>Tot. netto 12y</t>
-        </is>
+      <c r="D15" s="21">
+        <f>"Cedole nette "&amp;$B$10&amp;"y"</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>"Tot. netto "&amp;$B$10&amp;"y"</f>
+        <v/>
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
@@ -5216,10 +5143,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Bassa (PIL 1,5%)</t>
-        </is>
+      <c r="A16" s="8">
+        <f>"Bassa (PIL "&amp;SUBSTITUTE(ROUND(B16*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B16" s="12" t="n">
         <v>0.015</v>
@@ -5242,10 +5168,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Base (PIL 3,0%)</t>
-        </is>
+      <c r="A17" s="8">
+        <f>"Base (PIL "&amp;SUBSTITUTE(ROUND(B17*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B17" s="12" t="n">
         <v>0.03</v>
@@ -5268,10 +5193,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Alta (PIL 4,5%)</t>
-        </is>
+      <c r="A18" s="8">
+        <f>"Alta (PIL "&amp;SUBSTITUTE(ROUND(B18*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B18" s="12" t="n">
         <v>0.045</v>
@@ -5300,24 +5224,22 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>La tabella sopra RICOSTRUISCE il collocamento nov 2021 (chi sottoscrisse a 100 con premio PIL). Struttura step-up 4+4+4 anni DEFINITIVA 4a emissione (1-4: 0,75%, 5-8: 1,35%, 9-12: 1,70%). Per chi compra OGGI vale la sezione qui sotto: prezzo MOT 86,15 e NIENTE premio PIL.</t>
-        </is>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="10">
+        <f>"La tabella sopra RICOSTRUISCE il collocamento nov 2021 (chi sottoscrisse a 100 con premio PIL). Struttura step-up 4+4+4 anni DEFINITIVA 4a emissione (1-4: "&amp;SUBSTITUTE(ROUND(B5*100,2)&amp;"",".",",")&amp;"%, 5-8: "&amp;SUBSTITUTE(ROUND(B6*100,2)&amp;"",".",",")&amp;"%, 9-12: "&amp;SUBSTITUTE(ROUND(B7*100,2)&amp;"",".",",")&amp;"%). Per chi compra OGGI vale la sezione qui sotto: prezzo MOT "&amp;SUBSTITUTE(ROUND(B24,2)&amp;"",".",",")&amp;" e NIENTE premio PIL."</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Comprato OGGI sul MOT - prezzo 86,15 → YTM lordo ~3,65%</t>
-        </is>
+      <c r="A23" s="7">
+        <f>"Comprato OGGI sul MOT - prezzo "&amp;SUBSTITUTE(ROUND(B24,2)&amp;"",".",",")&amp;" → YTM lordo ~"&amp;SUBSTITUTE(ROUND(B27*100,2)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Prezzo MOT (uff. 09/06/2026)</t>
+          <t>Prezzo MOT corrente (vedi foglio Parametri)</t>
         </is>
       </c>
       <c r="B24" s="23">
@@ -5359,21 +5281,19 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>YTM netto (tassazione 12,5%)</t>
-        </is>
+      <c r="A28" s="8">
+        <f>"YTM netto (tassazione "&amp;SUBSTITUTE(ROUND(B11*100,1)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B28" s="16">
         <f>B27*(1-B11)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Il forte sconto sotto par (86,15) compensa le cedole basse: quasi tutto il rendimento arriva dal capital gain a scadenza (100-86,15 su 7,4 anni). ATTENZIONE: il doppio premio PIL spetta SOLO ai sottoscrittori originali del nov 2021, NON a chi compra sul MOT — il YTM qui sopra correttamente lo esclude.</t>
-        </is>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="10">
+        <f>"Lo sconto/premio sul prezzo MOT corrente ("&amp;SUBSTITUTE(ROUND(B24,2)&amp;"",".",",")&amp;") si somma alle cedole: parte del rendimento arriva dal capital gain a scadenza (100 - "&amp;SUBSTITUTE(ROUND(B24,2)&amp;"",".",",")&amp;" su "&amp;SUBSTITUTE(ROUND(B25,1)&amp;"",".",",")&amp;" anni). ATTENZIONE: il doppio premio PIL spetta SOLO ai sottoscrittori originali del nov 2021, NON a chi compra sul MOT — il YTM qui sopra correttamente lo esclude."</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -5401,10 +5321,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>1 - Disinflazione 1,0%</t>
-        </is>
+      <c r="A33" s="8">
+        <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B33" s="19">
         <f>'1 - Parametri'!B37</f>
@@ -5416,10 +5335,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>2 - Base BCE 2,0%</t>
-        </is>
+      <c r="A34" s="8">
+        <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B34" s="19">
         <f>'1 - Parametri'!B38</f>
@@ -5431,10 +5349,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>3 - Persistente 3,0%</t>
-        </is>
+      <c r="A35" s="8">
+        <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B35" s="19">
         <f>'1 - Parametri'!B39</f>
@@ -5446,10 +5363,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>4 - Stress geopol. 4,5%</t>
-        </is>
+      <c r="A36" s="8">
+        <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
       <c r="B36" s="19">
         <f>'1 - Parametri'!B40</f>
@@ -5568,7 +5484,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Tassazione 12,5% applicata</t>
+          <t>Tassazione titoli di Stato applicata</t>
         </is>
       </c>
       <c r="B6" s="19">
@@ -5719,7 +5635,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Rendimento certo in nominale. Se inflazione &gt; rendimento, perdi potere d'acquisto. Vantaggio: tassi attualmente alti, e plusvalenza se i tassi BCE scendono.</t>
+          <t>Rendimento certo in nominale. Se inflazione &gt; rendimento, perdi potere d'acquisto. Vantaggio: rendimento bloccato a scadenza, e possibile plusvalenza se i tassi BCE scendono.</t>
         </is>
       </c>
     </row>
@@ -5779,47 +5695,42 @@
           <t>Strumento</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>Infl. 1,0%</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>Infl. 2,0%</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>Infl. 3,0%</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>Infl. 4,5%</t>
-        </is>
+      <c r="B5" s="21">
+        <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="C5" s="21">
+        <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>BTP Italia Si (1,2% + FOI)</t>
-        </is>
+      <c r="A6" s="8">
+        <f>"BTP Italia Si ("&amp;SUBSTITUTE(ROUND('1 - Parametri'!B5*100,1)&amp;"",".",",")&amp;"% + FOI)"</f>
+        <v/>
       </c>
       <c r="B6" s="16">
-        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B37)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37,6)</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7/'1 - Parametri'!B6)+'1 - Parametri'!B37)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37,6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B38)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38,6)</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7/'1 - Parametri'!B6)+'1 - Parametri'!B38)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B38,6)</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B39)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39,6)</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7/'1 - Parametri'!B6)+'1 - Parametri'!B39)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B39,6)</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7)/5+'1 - Parametri'!B40)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40,6)</f>
+        <f>ROUND(('1 - Parametri'!B5+('1 - Parametri'!B7/'1 - Parametri'!B6)+'1 - Parametri'!B40)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B40,6)</f>
         <v/>
       </c>
     </row>
@@ -5847,10 +5758,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>BTP Valore (YTM lordo MOT ~3,48%)</t>
-        </is>
+      <c r="A8" s="8">
+        <f>"BTP Valore (YTM lordo MOT ~"&amp;SUBSTITUTE(ROUND('4 - BTP Valore'!$B$32*100,2)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B8" s="16">
         <f>'4 - BTP Valore'!$B$32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
@@ -5870,10 +5780,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>BTP Futura (YTM lordo MOT ~3,65%)</t>
-        </is>
+      <c r="A9" s="8">
+        <f>"BTP Futura (YTM lordo MOT ~"&amp;SUBSTITUTE(ROUND('5 - BTP Futura'!$B$27*100,2)&amp;"",".",",")&amp;"%)"</f>
+        <v/>
       </c>
       <c r="B9" s="16">
         <f>'5 - BTP Futura'!$B$27*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
@@ -5893,10 +5802,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>BTP nominale 5y (2,90% lordo)</t>
-        </is>
+      <c r="A10" s="8">
+        <f>"BTP nominale 5y ("&amp;SUBSTITUTE(ROUND('1 - Parametri'!B32*100,2)&amp;"",".",",")&amp;"% lordo)"</f>
+        <v/>
       </c>
       <c r="B10" s="16">
         <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
@@ -5916,10 +5824,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>BTP nominale 10y (3,45% lordo)</t>
-        </is>
+      <c r="A11" s="8">
+        <f>"BTP nominale 10y ("&amp;SUBSTITUTE(ROUND('1 - Parametri'!B34*100,2)&amp;"",".",",")&amp;"% lordo)"</f>
+        <v/>
       </c>
       <c r="B11" s="16">
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-'1 - Parametri'!B37</f>
@@ -5945,10 +5852,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>BTP Italia Si vince in scenari di inflazione media-alta perche' il tasso fisso e' REALE. BTP Italia classico in inflazione alta ha vantaggio capitale rivalutato. Valore e Futura: YTM da prezzo MOT (comprati OGGI, senza premi fedelta'/PIL), cedola nominale fissa → vincono solo con inflazione bassa. Nominali: vincono solo in disinflazione.</t>
+          <t>NOTA DI METODO - heatmap per colonna: VERDE = miglior rendimento REALE dello scenario, ROSSO = peggiore. Il tasso del Si e' REALE (si somma al FOI), quindi il suo rendimento reale resta stabile tra gli scenari; gli strumenti a cedola nominale fissa perdono rendimento reale al crescere dell'inflazione. Valore e Futura sono valutati allo YTM da prezzo MOT (comprati OGGI, senza premi fedelta'/PIL). Il vincitore di ogni scenario dipende dai parametri correnti del foglio 1 - Parametri.</t>
         </is>
       </c>
     </row>
@@ -6063,7 +5970,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>Rend. netto (1-12,5%)</t>
+          <t>Rend. netto (dopo tasse)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -6092,11 +5999,11 @@
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B6-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E6" s="24">
-        <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D6*100,2)&amp;"%"))</f>
+        <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D6*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -6115,11 +6022,11 @@
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B7-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E7" s="24">
-        <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D7*100,2)&amp;"%"))</f>
+        <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D7*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -6138,11 +6045,11 @@
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B8-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E8" s="24">
-        <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D8*100,2)&amp;"%"))</f>
+        <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D8*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -6161,11 +6068,11 @@
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B9-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E9" s="24">
-        <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D9*100,2)&amp;"%"))</f>
+        <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D9*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -6184,19 +6091,18 @@
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B10-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E10" s="24">
-        <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D10*100,2)&amp;"%"))</f>
+        <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D10*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>BTP Valore (YTM lordo MOT 98,65)</t>
-        </is>
+      <c r="A11" s="8">
+        <f>"BTP Valore (YTM lordo MOT, prezzo "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B64,2)&amp;"",".",",")&amp;")"</f>
+        <v/>
       </c>
       <c r="B11" s="16">
         <f>'4 - BTP Valore'!B32</f>
@@ -6207,19 +6113,18 @@
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B11-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E11" s="24">
-        <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D11*100,2)&amp;"%"))</f>
+        <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D11*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>BTP Futura (YTM lordo MOT 86,15)</t>
-        </is>
+      <c r="A12" s="8">
+        <f>"BTP Futura (YTM lordo MOT, prezzo "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B66,2)&amp;"",".",",")&amp;")"</f>
+        <v/>
       </c>
       <c r="B12" s="16">
         <f>'5 - BTP Futura'!B27</f>
@@ -6230,11 +6135,11 @@
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-('1 - Parametri'!B5+('1 - Parametri'!B7)/5)</f>
+        <f>B12-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
       <c r="E12" s="24">
-        <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;=0.045,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;ROUND(D12*100,2)&amp;"%"))</f>
+        <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D12*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
     </row>
@@ -6283,7 +6188,7 @@
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="D16" s="16">
@@ -6306,7 +6211,7 @@
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="D17" s="16">
@@ -6329,7 +6234,7 @@
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/5)*(1-'1 - Parametri'!B8)</f>
+        <f>('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)*(1-'1 - Parametri'!B8)</f>
         <v/>
       </c>
       <c r="D18" s="16">
@@ -6341,18 +6246,16 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>ATTENZIONE: usato YTM REALE EFFETTIVO calcolato dal prezzo MOT (non cedola del prospetto). Se sul secondario il classico quota SOPRA par, il YTM reale si abbassa, specie per scadenze brevi. Esempio coi prezzi uff. 09/06/2026: mar 2028 a 101,97 → YTM reale ~0,9%; giu 2030 a 101,92 → ~1,1%. Vai al foglio Parametri righe 46-56 per modificare i prezzi MOT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>BTP Futura comprato OGGI sul MOT a 86,15 (forte sconto sotto par): YTM lordo ~3,65% nonostante le cedole step-up basse (0,75/1,35/1,70). Soglia break-even FOI ~2,3%: sotto, il Futura vince; sopra, vince il Sì. Il doppio premio PIL NON spetta a chi compra sul MOT (solo sottoscrittori originali nov 2021).</t>
-        </is>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="10">
+        <f>"ATTENZIONE: usato YTM REALE EFFETTIVO calcolato dal prezzo MOT (non cedola del prospetto). Se sul secondario il classico quota SOPRA par, il YTM reale si abbassa, specie per scadenze brevi. Coi prezzi MOT correnti: mar 2028 a "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B46,2)&amp;"",".",",")&amp;" → YTM reale ~"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B50*100,2)&amp;"",".",",")&amp;"%; giu 2030 a "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B48,2)&amp;"",".",",")&amp;" → ~"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B52*100,2)&amp;"",".",",")&amp;"%. Vai al foglio Parametri righe 46-56 per modificare i prezzi MOT."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="10">
+        <f>"BTP Futura comprato OGGI sul MOT a "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B66,2)&amp;"",".",",")&amp;": YTM lordo ~"&amp;SUBSTITUTE(ROUND('5 - BTP Futura'!B27*100,2)&amp;"",".",",")&amp;"% con cedole step-up "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B22*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B23*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B24*100,2)&amp;"",".",",")&amp;"%. Soglia break-even FOI ~"&amp;SUBSTITUTE(ROUND(D12*100,2)&amp;"",".",",")&amp;"% (col. D): sotto la soglia vince il Futura, sopra vince il Si; se la soglia e' negativa il Si vince sempre. Il doppio premio PIL NON spetta a chi compra sul MOT (solo sottoscrittori originali nov 2021)."</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -18,6 +18,7 @@
     <sheet name="8 - Break-even" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11 - Flusso cedolare" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -210,6 +211,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -379,6 +383,130 @@
                 </a:pPr>
                 <a:r>
                   <a:t>IRR netto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <layout>
+            <manualLayout>
+              <xMode val="edge"/>
+              <yMode val="edge"/>
+              <wMode val="factor"/>
+              <hMode val="factor"/>
+              <x val="0.005"/>
+              <y val="0.3"/>
+            </manualLayout>
+          </layout>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0.00%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cedole nette semestrali + premio finale</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'11 - Flusso cedolare'!E12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'11 - Flusso cedolare'!$B$13:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'11 - Flusso cedolare'!$E$13:$E$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="4500">
+              <a:solidFill>
+                <a:srgbClr val="D0D0D0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>EUR netti</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1785,6 +1913,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2290,7 +2445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2435,116 +2590,128 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11 - Flusso cedolare</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Calendario semestrale: quanto incassi e quando, cedola per cedola</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Come usare</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>1. Le celle GIALLE sono input — modificale coi tuoi numeri.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2. Le celle VERDI sono output — si aggiornano automaticamente.</t>
+          <t>1. Le celle GIALLE sono input — modificale coi tuoi numeri.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>3. Tutti i numeri di default sono al 2026 da fonti pubbliche.</t>
+          <t>2. Le celle VERDI sono output — si aggiornano automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>3. Tutti i numeri di default sono al 2026 da fonti pubbliche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>4. Niente codice nascosto: l'Excel è solo formule modificabili.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Fonti dati</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>• MEF Dipartimento del Tesoro - Annuncio BTP Italia Si dal 15 al 19 giugno 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5">
-        <f>"• MEF - BTP Italia marzo 2028 (IT0005532723, scad. 14/03/2028) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B11*100,1)&amp;"",".",",")&amp;"%; giugno 2030 (IT0005497000) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B12*100,1)&amp;"",".",",")&amp;"%"</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5">
-        <f>"• MEF - BTP Valore marzo 2026 (IT0005696338) step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B15*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B16*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B17*100,2)&amp;"",".",",")&amp;"% + premio "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B18*100,1)&amp;"",".",",")&amp;"%, scadenza 10 mar 2032"</f>
+        <f>"• MEF - BTP Italia marzo 2028 (IT0005532723, scad. 14/03/2028) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B11*100,1)&amp;"",".",",")&amp;"%; giugno 2030 (IT0005497000) tasso reale "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B12*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5">
-        <f>"• MEF - BTP Futura 4a emissione nov 2021 (IT0005466351), "&amp;'1 - Parametri'!B27&amp;" anni step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B22*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B23*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B24*100,2)&amp;"",".",",")&amp;"% + doppio premio PIL (solo sottoscrittori originali), scadenza 16 nov 2033"</f>
+        <f>"• MEF - BTP Valore marzo 2026 (IT0005696338) step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B15*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B16*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B17*100,2)&amp;"",".",",")&amp;"% + premio "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B18*100,1)&amp;"",".",",")&amp;"%, scadenza 10 mar 2032"</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5">
+        <f>"• MEF - BTP Futura 4a emissione nov 2021 (IT0005466351), "&amp;'1 - Parametri'!B27&amp;" anni step-up DEFINITIVI "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B22*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B23*100,2)&amp;"",".",",")&amp;"/"&amp;SUBSTITUTE(ROUND('1 - Parametri'!B24*100,2)&amp;"",".",",")&amp;"% + doppio premio PIL (solo sottoscrittori originali), scadenza 16 nov 2033"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5">
         <f>"• Borsa Italiana MOT - prezzi ufficiali correnti (foglio 1 - Parametri): mar 2028 "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B46,2)&amp;"",".",",")&amp;"; giu 2030 "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B48,2)&amp;"",".",",")&amp;"; Valore "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B64,2)&amp;"",".",",")&amp;"; Futura "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B66,2)&amp;"",".",",")</f>
         <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>• MEF Tesoro - Calendario aste BTP nominali maggio 2026 (asta 13 e 28 maggio)</t>
-        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>• Banca d'Italia - Risultati aste BTP nominali 2026 (rendimenti curva 2y-10y)</t>
+          <t>• MEF Tesoro - Calendario aste BTP nominali maggio 2026 (asta 13 e 28 maggio)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>• ISTAT - Indice FOI per famiglie operai e impiegati (escluso tabacchi) - meccanismo BTP Italia</t>
+          <t>• Banca d'Italia - Risultati aste BTP nominali 2026 (rendimenti curva 2y-10y)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>• Eurostat - HICP eurozona per BTPi (non incluso in matrice; alternativa istituzionale)</t>
+          <t>• ISTAT - Indice FOI per famiglie operai e impiegati (escluso tabacchi) - meccanismo BTP Italia</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>• Eurostat - HICP eurozona per BTPi (non incluso in matrice; alternativa istituzionale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>• Borsa Italiana MOT - mercato secondario BTP retail (liquidita' supportata da Dealer MEF)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Aggiornamenti: github.com/marcofire-it/marco-fire-simulatori</t>
         </is>
@@ -3022,6 +3189,490 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BTP Italia Si - flusso cedolare semestrale (quanto incassi, quando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Strumento informativo / divulgativo. NON è consulenza finanziaria. I valori sono indicativi al 2026 e vanno verificati col tuo consulente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Input (tasso/premio/tassazione dal foglio Parametri; FOI modificabile QUI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Tasso fisso reale annuo</t>
+        </is>
+      </c>
+      <c r="B5" s="16">
+        <f>'1 - Parametri'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Premio fedelta' finale</t>
+        </is>
+      </c>
+      <c r="B6" s="16">
+        <f>'1 - Parametri'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Tassazione</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>'1 - Parametri'!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Capitale investito (EUR)</t>
+        </is>
+      </c>
+      <c r="B8" s="20">
+        <f>'1 - Parametri'!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Inflazione FOI media (scenario)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>GIALLO = modificabile: 0,01 / 0,02 / 0,03 / 0,045</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Calendario cedole semestrali nette (convenzione lineare, FOI media costante)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Stacco</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Cedola lorda</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Imposta</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Cedola netta</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Cumulato netto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>dic 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>C13*$B$7</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>giu 2027</t>
+        </is>
+      </c>
+      <c r="C14" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D14" s="27">
+        <f>C14*$B$7</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>F13+E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>dic 2027</t>
+        </is>
+      </c>
+      <c r="C15" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>C15*$B$7</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>F14+E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>giu 2028</t>
+        </is>
+      </c>
+      <c r="C16" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>C16*$B$7</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>F15+E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>dic 2028</t>
+        </is>
+      </c>
+      <c r="C17" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>C17*$B$7</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>F16+E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>giu 2029</t>
+        </is>
+      </c>
+      <c r="C18" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>C18*$B$7</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>F17+E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>dic 2029</t>
+        </is>
+      </c>
+      <c r="C19" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>C19*$B$7</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>F18+E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>giu 2030</t>
+        </is>
+      </c>
+      <c r="C20" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>C20*$B$7</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="27">
+        <f>F19+E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>dic 2030</t>
+        </is>
+      </c>
+      <c r="C21" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>C21*$B$7</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>C21-D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="27">
+        <f>F20+E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>giu 2031</t>
+        </is>
+      </c>
+      <c r="C22" s="27">
+        <f>($B$5+$B$9)/2*$B$8</f>
+        <v/>
+      </c>
+      <c r="D22" s="27">
+        <f>C22*$B$7</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>C22-D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="27">
+        <f>F21+E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Premio</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>giu 2031</t>
+        </is>
+      </c>
+      <c r="C24" s="27">
+        <f>$B$8*$B$6</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>C24*$B$7</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>C24-D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="27">
+        <f>F22+E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>TOTALE NETTO 5 ANNI (cedole + premio)</t>
+        </is>
+      </c>
+      <c r="F25" s="27">
+        <f>F24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Note metodologiche</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Date indicative: godimento giugno 2026, cedole semestrali dicembre/giugno. Il FOI media e' un'ipotesi di scenario: le cedole effettive varieranno semestre per semestre con l'inflazione FOI rilevata da ISTAT. Il premio fedelta' spetta solo a chi sottoscrive in collocamento e tiene fino a scadenza.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -439,6 +439,7 @@
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -523,17 +524,13 @@
           </layout>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="0.00%" sourceLinked="0"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -27,10 +27,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="mmm aaaa"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -143,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -213,7 +214,13 @@
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,12 +462,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'11 - Flusso cedolare'!$B$13:$B$24</f>
+              <f>'11 - Flusso cedolare'!$A$13:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'11 - Flusso cedolare'!$E$13:$E$24</f>
+              <f>'11 - Flusso cedolare'!$E$13:$E$23</f>
             </numRef>
           </val>
         </ser>
@@ -1914,7 +1921,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -3197,15 +3204,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -3326,6 +3334,11 @@
           <t>Cumulato netto</t>
         </is>
       </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Flusso di cassa</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -3333,24 +3346,26 @@
           <t>1/10</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>dic 2026</t>
-        </is>
-      </c>
-      <c r="C13" s="27">
+      <c r="B13" s="29" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C13" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>C13*$B$7</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
         <f>E13</f>
         <v/>
       </c>
@@ -3361,25 +3376,27 @@
           <t>2/10</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>giu 2027</t>
-        </is>
-      </c>
-      <c r="C14" s="27">
+      <c r="B14" s="29" t="n">
+        <v>46553</v>
+      </c>
+      <c r="C14" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>C14*$B$7</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>F13+E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
+        <f>E14</f>
         <v/>
       </c>
     </row>
@@ -3389,25 +3406,27 @@
           <t>3/10</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>dic 2027</t>
-        </is>
-      </c>
-      <c r="C15" s="27">
+      <c r="B15" s="29" t="n">
+        <v>46736</v>
+      </c>
+      <c r="C15" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>C15*$B$7</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="28">
         <f>F14+E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="28">
+        <f>E15</f>
         <v/>
       </c>
     </row>
@@ -3417,25 +3436,27 @@
           <t>4/10</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>giu 2028</t>
-        </is>
-      </c>
-      <c r="C16" s="27">
+      <c r="B16" s="29" t="n">
+        <v>46919</v>
+      </c>
+      <c r="C16" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>C16*$B$7</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>C16-D16</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>F15+E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>E16</f>
         <v/>
       </c>
     </row>
@@ -3445,25 +3466,27 @@
           <t>5/10</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>dic 2028</t>
-        </is>
-      </c>
-      <c r="C17" s="27">
+      <c r="B17" s="29" t="n">
+        <v>47102</v>
+      </c>
+      <c r="C17" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>C17*$B$7</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>F16+E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="28">
+        <f>E17</f>
         <v/>
       </c>
     </row>
@@ -3473,25 +3496,27 @@
           <t>6/10</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>giu 2029</t>
-        </is>
-      </c>
-      <c r="C18" s="27">
+      <c r="B18" s="29" t="n">
+        <v>47284</v>
+      </c>
+      <c r="C18" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>C18*$B$7</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <f>F17+E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="28">
+        <f>E18</f>
         <v/>
       </c>
     </row>
@@ -3501,25 +3526,27 @@
           <t>7/10</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>dic 2029</t>
-        </is>
-      </c>
-      <c r="C19" s="27">
+      <c r="B19" s="29" t="n">
+        <v>47467</v>
+      </c>
+      <c r="C19" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>C19*$B$7</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>F18+E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="28">
+        <f>E19</f>
         <v/>
       </c>
     </row>
@@ -3529,25 +3556,27 @@
           <t>8/10</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>giu 2030</t>
-        </is>
-      </c>
-      <c r="C20" s="27">
+      <c r="B20" s="29" t="n">
+        <v>47649</v>
+      </c>
+      <c r="C20" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>C20*$B$7</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="28">
         <f>F19+E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>E20</f>
         <v/>
       </c>
     </row>
@@ -3557,25 +3586,27 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>dic 2030</t>
-        </is>
-      </c>
-      <c r="C21" s="27">
+      <c r="B21" s="29" t="n">
+        <v>47832</v>
+      </c>
+      <c r="C21" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>C21*$B$7</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <f>F20+E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="28">
+        <f>E21</f>
         <v/>
       </c>
     </row>
@@ -3585,90 +3616,163 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>giu 2031</t>
-        </is>
-      </c>
-      <c r="C22" s="27">
+      <c r="B22" s="29" t="n">
+        <v>48014</v>
+      </c>
+      <c r="C22" s="28">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>C22*$B$7</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="28">
         <f>F21+E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Premio</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="n">
+        <v>48014</v>
+      </c>
+      <c r="C23" s="28">
+        <f>$B$8*$B$6</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>C23*$B$7</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>C23-D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="28">
+        <f>F22+E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="28">
+        <f>E23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Premio</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>giu 2031</t>
-        </is>
-      </c>
-      <c r="C24" s="27">
-        <f>$B$8*$B$6</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>C24*$B$7</f>
-        <v/>
-      </c>
-      <c r="E24" s="27">
-        <f>C24-D24</f>
-        <v/>
-      </c>
-      <c r="F24" s="27">
-        <f>F22+E24</f>
+          <t>Acquisto</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G24" s="28">
+        <f>-$B$8</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>Rimborso</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="n">
+        <v>48014</v>
+      </c>
+      <c r="G25" s="28">
+        <f>$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>TOTALE NETTO 5 ANNI (cedole + premio)</t>
         </is>
       </c>
-      <c r="F25" s="27">
-        <f>F24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="F26" s="28">
+        <f>F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>IRR dai flussi di cassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>IRR nominale netto EFFETTIVO (XIRR composto sui flussi)</t>
+        </is>
+      </c>
+      <c r="F29" s="16">
+        <f>XIRR(G13:G25,B13:B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>IRR nominale netto LINEARE (convenzione fogli 2-7)</t>
+        </is>
+      </c>
+      <c r="F30" s="16">
+        <f>ROUND(($B$5+$B$6/'1 - Parametri'!B6+$B$9)*(1-$B$7),6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>IRR REALE netto effettivo (XIRR - FOI media)</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <f>F29-$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Note metodologiche</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Date indicative: godimento giugno 2026, cedole semestrali dicembre/giugno. Il FOI media e' un'ipotesi di scenario: le cedole effettive varieranno semestre per semestre con l'inflazione FOI rilevata da ISTAT. Il premio fedelta' spetta solo a chi sottoscrive in collocamento e tiene fino a scadenza.</t>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Date indicative: godimento giugno 2026, cedole semestrali dicembre/giugno (15 del mese convenzionale; acquisto = chiusura collocamento 19/06/2026). Il FOI media e' un'ipotesi di scenario: le cedole effettive varieranno semestre per semestre con l'inflazione FOI rilevata da ISTAT. Il premio fedelta' spetta solo a chi sottoscrive in collocamento e tiene fino a scadenza. XIRR = rendimento composto effettivo sui flussi datati; differisce di pochi centesimi dall'IRR lineare divulgativo usato negli altri fogli (che non compone i reinvestimenti).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A4:F4"/>
+  <mergeCells count="8">
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="D30" s="10">
         <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B30*100,2)&amp;"",".",",")&amp;"%"</f>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="D31" s="10">
         <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B31*100,2)&amp;"",".",",")&amp;"%"</f>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.029</v>
+        <v>0.0313</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.0315</v>
+        <v>0.0344</v>
       </c>
       <c r="D33" s="10">
         <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B33*100,2)&amp;"",".",",")&amp;"%"</f>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.0345</v>
+        <v>0.0374</v>
       </c>
       <c r="D34" s="10">
         <f>"MEF asta: "&amp;SUBSTITUTE(ROUND(B34*100,2)&amp;"",".",",")&amp;"%"</f>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>101.97</v>
+        <v>101.83</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>101.92</v>
+        <v>101.86</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="B64" s="14" t="n">
-        <v>98.65000000000001</v>
+        <v>99.03</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B66" s="14" t="n">
-        <v>86.15000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -27,11 +27,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000%"/>
-    <numFmt numFmtId="167" formatCode="mmm aaaa"/>
+    <numFmt numFmtId="166" formatCode="0.0000%"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="mmm aaaa"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -144,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,6 +188,9 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -199,7 +203,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,13 +218,13 @@
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2769,32 +2773,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Profilo</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>BTP Italia Si</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>BTP Italia clas.</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>BTP Valore</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>BTP nominale 5y</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>BTP nominale 10y</t>
         </is>
@@ -2806,19 +2810,19 @@
           <t>Giovane 25-34</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2828,19 +2832,19 @@
           <t>Mezza età 35-49</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -2850,19 +2854,19 @@
           <t>Over 50 pre-FIRE</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2872,19 +2876,19 @@
           <t>FIRE in decumulo</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3022,7 +3026,7 @@
           <t>Tua aliquota IRPEF marginale (info)</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -3034,17 +3038,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Strumento</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Rend. reale annuo</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Idoneo al tuo orizzonte</t>
         </is>
@@ -3060,7 +3064,7 @@
         <f>('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -3075,7 +3079,7 @@
         <f>'1 - Parametri'!B56*(1-'1 - Parametri'!B8)-'1 - Parametri'!B8*B7</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -3090,7 +3094,7 @@
         <f>'4 - BTP Valore'!B32*(1-'1 - Parametri'!B8)-B7</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <f>IF(B6&gt;=6,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -3105,7 +3109,7 @@
         <f>'1 - Parametri'!B32*(1-'1 - Parametri'!B8)-B7</f>
         <v/>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <f>IF(B6&gt;=5,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -3120,7 +3124,7 @@
         <f>'1 - Parametri'!B34*(1-'1 - Parametri'!B8)-B7</f>
         <v/>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <f>IF(B6&gt;=10,"SI","NO - troppo lungo")</f>
         <v/>
       </c>
@@ -3138,7 +3142,7 @@
           <t>Miglior strumento</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="25">
         <f>INDEX(A12:A16,MATCH(MAX(B12:B16),B12:B16,0))</f>
         <v/>
       </c>
@@ -3160,7 +3164,7 @@
           <t>Valore finale (con cap. + reale)</t>
         </is>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="21">
         <f>B5*(1+B20)^B6</f>
         <v/>
       </c>
@@ -3265,7 +3269,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -3276,7 +3280,7 @@
           <t>Capitale investito (EUR)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -3304,37 +3308,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Stacco</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Cedola lorda</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>Imposta</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Cedola netta</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>Cumulato netto</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>Flusso di cassa</t>
         </is>
@@ -3346,26 +3350,26 @@
           <t>1/10</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="30" t="n">
         <v>46371</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>C13*$B$7</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>E13</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>E13</f>
         <v/>
       </c>
@@ -3376,26 +3380,26 @@
           <t>2/10</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <v>46553</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <f>C14*$B$7</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>F13+E14</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>E14</f>
         <v/>
       </c>
@@ -3406,26 +3410,26 @@
           <t>3/10</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>46736</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>C15*$B$7</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F14+E15</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>E15</f>
         <v/>
       </c>
@@ -3436,26 +3440,26 @@
           <t>4/10</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>46919</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>C16*$B$7</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>C16-D16</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F15+E16</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>E16</f>
         <v/>
       </c>
@@ -3466,26 +3470,26 @@
           <t>5/10</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>47102</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <f>C17*$B$7</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="29">
         <f>C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <f>F16+E17</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <f>E17</f>
         <v/>
       </c>
@@ -3496,26 +3500,26 @@
           <t>6/10</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>47284</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>C18*$B$7</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>F17+E18</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f>E18</f>
         <v/>
       </c>
@@ -3526,26 +3530,26 @@
           <t>7/10</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>47467</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>C19*$B$7</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <f>C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <f>F18+E19</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <f>E19</f>
         <v/>
       </c>
@@ -3556,26 +3560,26 @@
           <t>8/10</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>47649</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <f>C20*$B$7</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <f>C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <f>F19+E20</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="29">
         <f>E20</f>
         <v/>
       </c>
@@ -3586,26 +3590,26 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>47832</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>C21*$B$7</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>F20+E21</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>E21</f>
         <v/>
       </c>
@@ -3616,26 +3620,26 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>48014</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>($B$5+$B$9)/2*$B$8</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>C22*$B$7</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>F21+E22</f>
         <v/>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>E22</f>
         <v/>
       </c>
@@ -3646,26 +3650,26 @@
           <t>Premio</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>48014</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>$B$8*$B$6</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>C23*$B$7</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F22+E23</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>E23</f>
         <v/>
       </c>
@@ -3676,10 +3680,10 @@
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>46192</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <f>-$B$8</f>
         <v/>
       </c>
@@ -3690,10 +3694,10 @@
           <t>Rimborso</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>48014</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <f>$B$8</f>
         <v/>
       </c>
@@ -3704,7 +3708,7 @@
           <t>TOTALE NETTO 5 ANNI (cedole + premio)</t>
         </is>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="29">
         <f>F23</f>
         <v/>
       </c>
@@ -3785,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4301,7 +4305,7 @@
         </is>
       </c>
       <c r="B50" s="16">
-        <f>(B11*100+(100-B46)/D46)/((100+B46)/2)</f>
+        <f>(B11*100+(100-B46)/D46)/((100+B46)/2)+B76</f>
         <v/>
       </c>
     </row>
@@ -4318,7 +4322,7 @@
         </is>
       </c>
       <c r="B52" s="16">
-        <f>(B12*100+(100-B48)/D48)/((100+B48)/2)</f>
+        <f>(B12*100+(100-B48)/D48)/((100+B48)/2)+B77</f>
         <v/>
       </c>
     </row>
@@ -4523,8 +4527,62 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Calibrazione IRR esatto (auto: compute_ytm_exact.py + sync, NON modificare a mano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Offset IRR mar 2028 (esatto - BEY)</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>-0.000259</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Offset IRR giu 2030 (esatto - BEY)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>6.8e-05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Offset IRR BTP Valore (esatto - BEY)</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="n">
+        <v>0.000478</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Offset IRR BTP Futura (esatto - BEY)</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>0.00039</v>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Le formule YTM nei fogli sono bond-equivalent-yield + offset: ai prezzi correnti coincidono con l'IRR esatto da cashflow datati (stessi numeri di video e simulatore web).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A29:D29"/>
@@ -4539,6 +4597,8 @@
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A69:D69"/>
     <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A57:D57"/>
@@ -4606,7 +4666,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>'1 - Parametri'!B6</f>
         <v/>
       </c>
@@ -4628,7 +4688,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -4639,7 +4699,7 @@
           <t>Capitale investito (EUR)</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -4652,27 +4712,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Infl. FOI media</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Cedola lorda annua</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Importo netto su cap.</t>
         </is>
@@ -4683,7 +4743,7 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
@@ -4695,7 +4755,7 @@
         <f>C13*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>$B$9*D13</f>
         <v/>
       </c>
@@ -4705,7 +4765,7 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
@@ -4717,7 +4777,7 @@
         <f>C14*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>$B$9*D14</f>
         <v/>
       </c>
@@ -4727,7 +4787,7 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
@@ -4739,7 +4799,7 @@
         <f>C15*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>$B$9*D15</f>
         <v/>
       </c>
@@ -4749,7 +4809,7 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
@@ -4761,7 +4821,7 @@
         <f>C16*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>$B$9*D16</f>
         <v/>
       </c>
@@ -4773,31 +4833,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="22">
         <f>"Cedole nette tot "&amp;$B$6&amp;"y"</f>
         <v/>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Premio netto fedelta'</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Tot. netto incassato</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>IRR nom netto annuo (lineare)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>IRR reale netto</t>
         </is>
@@ -4808,15 +4868,15 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="21">
         <f>E13*$B$6</f>
         <v/>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <f>B20+C20</f>
         <v/>
       </c>
@@ -4834,15 +4894,15 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="21">
         <f>E14*$B$6</f>
         <v/>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <f>B21+C21</f>
         <v/>
       </c>
@@ -4860,15 +4920,15 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <f>E15*$B$6</f>
         <v/>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <f>B22+C22</f>
         <v/>
       </c>
@@ -4886,15 +4946,15 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="21">
         <f>E16*$B$6</f>
         <v/>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="21">
         <f>$B$9*$B$7*(1-$B$8)</f>
         <v/>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="21">
         <f>B23+C23</f>
         <v/>
       </c>
@@ -5012,7 +5072,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -5023,7 +5083,7 @@
           <t>Capitale investito (EUR)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -5036,25 +5096,25 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="22">
         <f>"FOI cumulata "&amp;$B$6&amp;"y"</f>
         <v/>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Capitale rivalutato</t>
         </is>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <f>"Cedole nette "&amp;$B$6&amp;"y (su cap. rivalut.)"</f>
         <v/>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <f>"Tot. netto "&amp;$B$6&amp;"y (cedole + rivalut.)"</f>
         <v/>
       </c>
@@ -5064,19 +5124,19 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>$B$8*(1+B12)^$B$6</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>$B$5*$B$8*((1+B12)^$B$6-1)/B12*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>(C12-$B$8)*(1-$B$7)+D12</f>
         <v/>
       </c>
@@ -5086,19 +5146,19 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>$B$8*(1+B13)^$B$6</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>$B$5*$B$8*((1+B13)^$B$6-1)/B13*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>(C13-$B$8)*(1-$B$7)+D13</f>
         <v/>
       </c>
@@ -5108,19 +5168,19 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>$B$8*(1+B14)^$B$6</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>$B$5*$B$8*((1+B14)^$B$6-1)/B14*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>(C14-$B$8)*(1-$B$7)+D14</f>
         <v/>
       </c>
@@ -5130,19 +5190,19 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>$B$8*(1+B15)^$B$6</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <f>$B$5*$B$8*((1+B15)^$B$6-1)/B15*(1-$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>(C15-$B$8)*(1-$B$7)+D15</f>
         <v/>
       </c>
@@ -5155,16 +5215,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="22">
         <f>"Tot. netto "&amp;$B$6&amp;"y"</f>
         <v/>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>IRR netto annuo</t>
         </is>
@@ -5175,7 +5235,7 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="21">
         <f>E12</f>
         <v/>
       </c>
@@ -5189,7 +5249,7 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="21">
         <f>E13</f>
         <v/>
       </c>
@@ -5203,7 +5263,7 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="21">
         <f>E14</f>
         <v/>
       </c>
@@ -5217,7 +5277,7 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <f>E15</f>
         <v/>
       </c>
@@ -5366,7 +5426,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'1 - Parametri'!B19</f>
         <v/>
       </c>
@@ -5377,7 +5437,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -5388,7 +5448,7 @@
           <t>Capitale investito</t>
         </is>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -5401,27 +5461,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Cedola lorda annua</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>Importo netto x anno</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Importo netto x fase (2y)</t>
         </is>
@@ -5436,15 +5496,15 @@
         <f>B5</f>
         <v/>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>B5*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <f>$B$11*C15</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>D15*2</f>
         <v/>
       </c>
@@ -5458,15 +5518,15 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <f>B6*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>$B$11*C16</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>D16*2</f>
         <v/>
       </c>
@@ -5480,15 +5540,15 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>B7*(1-$B$10)</f>
         <v/>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <f>$B$11*C17</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>D17*2</f>
         <v/>
       </c>
@@ -5504,7 +5564,7 @@
         <f>"Tot. cedole nette "&amp;B9&amp;"y"</f>
         <v/>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="21">
         <f>E15+E16+E17</f>
         <v/>
       </c>
@@ -5515,7 +5575,7 @@
           <t>Premio fedelta' netto</t>
         </is>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="21">
         <f>B11*B8*(1-B10)</f>
         <v/>
       </c>
@@ -5525,7 +5585,7 @@
         <f>"Tot. netto "&amp;B9&amp;"y"</f>
         <v/>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <f>B20+B21</f>
         <v/>
       </c>
@@ -5567,7 +5627,7 @@
           <t>Prezzo MOT corrente (vedi foglio Parametri)</t>
         </is>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="24">
         <f>'1 - Parametri'!B64</f>
         <v/>
       </c>
@@ -5578,7 +5638,7 @@
           <t>Anni residui (scad. 10/03/2032)</t>
         </is>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="24">
         <f>'1 - Parametri'!D64</f>
         <v/>
       </c>
@@ -5601,7 +5661,7 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>(B31*100+(100-B29)/B30)/((100+B29)/2)</f>
+        <f>(B31*100+(100-B29)/B30)/((100+B29)/2)+'1 - Parametri'!B78</f>
         <v/>
       </c>
     </row>
@@ -5629,17 +5689,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Infl. FOI media</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>IRR reale netto (YTM netto - FOI)</t>
         </is>
@@ -5650,7 +5710,7 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="20">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
@@ -5664,7 +5724,7 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="20">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
@@ -5678,7 +5738,7 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="20">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
@@ -5692,7 +5752,7 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="20">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
@@ -5830,7 +5890,7 @@
           <t>Durata (anni)</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'1 - Parametri'!B27</f>
         <v/>
       </c>
@@ -5841,7 +5901,7 @@
           <t>Tassazione</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -5852,7 +5912,7 @@
           <t>Capitale</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
@@ -5865,30 +5925,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Scenario PIL nominale medio</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>PIL nom. medio</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Premio fed. atteso</t>
         </is>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>"Cedole nette "&amp;$B$10&amp;"y"</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="22">
         <f>"Tot. netto "&amp;$B$10&amp;"y"</f>
         <v/>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>IRR nom netto annuo (lineare)</t>
         </is>
@@ -5906,11 +5966,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B16))</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>D16+$B$12*C16*(1-$B$11)</f>
         <v/>
       </c>
@@ -5931,11 +5991,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B17))</f>
         <v/>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>D17+$B$12*C17*(1-$B$11)</f>
         <v/>
       </c>
@@ -5956,11 +6016,11 @@
         <f>MAX($B$8,MIN($B$9,0.4*B18))</f>
         <v/>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>$B$12*(4*$B$5+4*$B$6+4*$B$7)*(1-$B$11)</f>
         <v/>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <f>D18+$B$12*C18*(1-$B$11)</f>
         <v/>
       </c>
@@ -5994,7 +6054,7 @@
           <t>Prezzo MOT corrente (vedi foglio Parametri)</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="24">
         <f>'1 - Parametri'!B66</f>
         <v/>
       </c>
@@ -6005,7 +6065,7 @@
           <t>Anni residui (scad. 16/11/2033)</t>
         </is>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="24">
         <f>'1 - Parametri'!D66</f>
         <v/>
       </c>
@@ -6028,7 +6088,7 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>(B26*100+(100-B24)/B25)/((100+B24)/2)</f>
+        <f>(B26*100+(100-B24)/B25)/((100+B24)/2)+'1 - Parametri'!B79</f>
         <v/>
       </c>
     </row>
@@ -6056,17 +6116,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Scenario inflazione</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>Infl. FOI media</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>IRR reale netto (YTM netto - FOI)</t>
         </is>
@@ -6077,7 +6137,7 @@
         <f>"1 - Disinflazione "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="20">
         <f>'1 - Parametri'!B37</f>
         <v/>
       </c>
@@ -6091,7 +6151,7 @@
         <f>"2 - Base BCE "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <f>'1 - Parametri'!B38</f>
         <v/>
       </c>
@@ -6105,7 +6165,7 @@
         <f>"3 - Persistente "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="20">
         <f>'1 - Parametri'!B39</f>
         <v/>
       </c>
@@ -6119,7 +6179,7 @@
         <f>"4 - Stress geopol. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="20">
         <f>'1 - Parametri'!B40</f>
         <v/>
       </c>
@@ -6207,27 +6267,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Scadenza</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Rendimento lordo</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Cedola netta annua</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Tot. cedole nette a scad.</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Cedola netta annua EUR</t>
         </is>
@@ -6239,7 +6299,7 @@
           <t>Tassazione titoli di Stato applicata</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>'1 - Parametri'!B8</f>
         <v/>
       </c>
@@ -6250,13 +6310,13 @@
           <t>Capitale (default Parametri)</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>'1 - Parametri'!B43</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Rendim. lordo (curva)</t>
         </is>
@@ -6272,15 +6332,15 @@
         <f>'1 - Parametri'!B30</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>B9*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>$B$7*C9*2</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>$B$7*C9</f>
         <v/>
       </c>
@@ -6295,15 +6355,15 @@
         <f>'1 - Parametri'!B31</f>
         <v/>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>B10*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>$B$7*C10*3</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>$B$7*C10</f>
         <v/>
       </c>
@@ -6318,15 +6378,15 @@
         <f>'1 - Parametri'!B32</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>B11*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>$B$7*C11*5</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>$B$7*C11</f>
         <v/>
       </c>
@@ -6341,15 +6401,15 @@
         <f>'1 - Parametri'!B33</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="23">
         <f>B12*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>$B$7*C12*7</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>$B$7*C12</f>
         <v/>
       </c>
@@ -6364,15 +6424,15 @@
         <f>'1 - Parametri'!B34</f>
         <v/>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>B13*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>$B$7*C13*10</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>$B$7*C13</f>
         <v/>
       </c>
@@ -6442,24 +6502,24 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Strumento</t>
         </is>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="22">
         <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B37*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B38*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="22">
         <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B39*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="22">
         <f>"Infl. "&amp;SUBSTITUTE(ROUND('1 - Parametri'!B40*100,1)&amp;"",".",",")&amp;"%"</f>
         <v/>
       </c>
@@ -6710,27 +6770,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Avversario</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Rendimento lordo</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Rend. netto (dopo tasse)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Soglia infl. break-even (lorda)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Verdetto</t>
         </is>
@@ -6754,7 +6814,7 @@
         <f>B6-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>IF(D6&lt;=0,"Si vince SEMPRE",IF(D6&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D6*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6777,7 +6837,7 @@
         <f>B7-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <f>IF(D7&lt;=0,"Si vince SEMPRE",IF(D7&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D7*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6800,7 +6860,7 @@
         <f>B8-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>IF(D8&lt;=0,"Si vince SEMPRE",IF(D8&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D8*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6823,7 +6883,7 @@
         <f>B9-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <f>IF(D9&lt;=0,"Si vince SEMPRE",IF(D9&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D9*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6846,7 +6906,7 @@
         <f>B10-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <f>IF(D10&lt;=0,"Si vince SEMPRE",IF(D10&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D10*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6868,7 +6928,7 @@
         <f>B11-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <f>IF(D11&lt;=0,"Si vince SEMPRE",IF(D11&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D11*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6890,7 +6950,7 @@
         <f>B12-('1 - Parametri'!B5+'1 - Parametri'!B7/'1 - Parametri'!B6)</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>IF(D12&lt;=0,"Si vince SEMPRE",IF(D12&gt;='1 - Parametri'!B40,"Si perde quasi sempre","Si vince se FOI &gt; "&amp;SUBSTITUTE(ROUND(D12*100,2)&amp;"",".",",")&amp;"%"))</f>
         <v/>
       </c>
@@ -6903,27 +6963,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Avversario</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>YTM reale NETTO (MOT)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Sì reale netto</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Vantaggio Sì (pp)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Verdetto</t>
         </is>
@@ -6947,7 +7007,7 @@
         <f>C16-B16</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>IF(D16&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D16*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D16*100,2)&amp;"pp)")</f>
         <v/>
       </c>
@@ -6970,7 +7030,7 @@
         <f>C17-B17</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>IF(D17&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D17*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D17*100,2)&amp;"pp)")</f>
         <v/>
       </c>
@@ -6993,7 +7053,7 @@
         <f>C18-B18</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>IF(D18&gt;=0,"Sì vince (vantaggio "&amp;ROUND(D18*100,2)&amp;"pp)","Classico vince (gap "&amp;ROUND(-D18*100,2)&amp;"pp)")</f>
         <v/>
       </c>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -19,6 +19,7 @@
     <sheet name="9 - 4 profili FIRE" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10 - Calcolatore personale" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11 - Flusso cedolare" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12 - Switch" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,12 +28,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.000%"/>
     <numFmt numFmtId="168" formatCode="mmm aaaa"/>
+    <numFmt numFmtId="169" formatCode="+0.00%;-0.00%;0.00%"/>
+    <numFmt numFmtId="170" formatCode="#,##0&quot; EUR&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -145,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +228,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -542,6 +551,267 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Break-even: quando conviene lo switch</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Vecchio (rend. reale)</v>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E0A458"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'12 - Switch'!$A$34:$A$41</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'12 - Switch'!$B$34:$B$41</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Nuovo Si (rend. reale)</v>
+          </tx>
+          <spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="10B981"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'12 - Switch'!$A$34:$A$41</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'12 - Switch'!$C$34:$C$41</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Prezzo di indifferenza</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="diamond"/>
+            <size val="12"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <tx>
+                <rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="it-IT" b="1" sz="1150">
+                        <a:solidFill>
+                          <a:srgbClr val="C00000"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>≈ 100,7</a:t>
+                    </a:r>
+                  </a:p>
+                </rich>
+              </tx>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'12 - Switch'!$B$24</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'12 - Switch'!$B$14</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Prezzo del vecchio (su 100)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <layout>
+            <manualLayout>
+              <xMode val="edge"/>
+              <yMode val="edge"/>
+              <wMode val="factor"/>
+              <hMode val="factor"/>
+              <x val="0.4"/>
+              <y val="0.93"/>
+            </manualLayout>
+          </layout>
+          <overlay val="0"/>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="3000">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Rendimento reale annuo</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <layout>
+            <manualLayout>
+              <xMode val="edge"/>
+              <yMode val="edge"/>
+              <wMode val="factor"/>
+              <hMode val="factor"/>
+              <x val="0.005"/>
+              <y val="0.3"/>
+            </manualLayout>
+          </layout>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1948,6 +2218,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7560000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -3783,6 +4080,371 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Switch: conviene vendere un vecchio BTP Italia per il nuovo Si?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Strumento informativo / divulgativo. NON è consulenza finanziaria. I valori sono indicativi al 2026 e vanno verificati col tuo consulente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Il tuo vecchio BTP Italia (quello che valuti di vendere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Nominale posseduto (EUR)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo MOT attuale (su 100)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>101.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Tasso reale del vecchio (% annuo)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>0.0185</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Anni residui alla scadenza</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Il nuovo BTP Italia Si (in emissione, a 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Tasso reale</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>'1 - Parametri'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Premio fedelta' (a scadenza)</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
+        <f>'1 - Parametri'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Durata (anni)</t>
+        </is>
+      </c>
+      <c r="B13" s="19">
+        <f>'1 - Parametri'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Rendimento reale annuo (comprato a 100)</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>B11+B12/B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Confronto: rendimento reale annuo DA OGGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Vecchio, tenuto a scadenza (sul prezzo attuale)</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>(B7*100+(100-B6)/B8)/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Nuovo Si (comprato a 100)</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Differenza annua (Si - vecchio)</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
+        <f>B18-B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Vantaggio stimato dello switch (su 5 anni)</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>B19*B13*(B5*B6/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Verdetto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Conviene lo switch?</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>IF(B18&gt;B17,"SI - valuta lo switch","NO - tieni il vecchio")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Prezzo di indifferenza del vecchio</t>
+        </is>
+      </c>
+      <c r="B24" s="24">
+        <f>(B7*100+100/B8)/(B18+1/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Logica: confronta il rendimento reale annuo che otterresti DA OGGI tenendo il vecchio (penalizzato se quota sopra 100, perche' a scadenza torna a 100) contro il Si comprato a 100. Se il vecchio quota SOPRA il prezzo di indifferenza, lo switch inizia ad avere senso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Attenzione: vendendo il vecchio perdi il rateo/rivalutazione gia' maturati e il suo premio fedelta'; paghi spread ed esecuzione. Per piccoli importi il vantaggio e' spesso di pochi euro. Stima semplificata (rendimento 'semplice', cedole non reinvestite). NON e' consulenza finanziaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Dati grafico break-even (prezzo del vecchio -&gt; rendimento reale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Prezzo vecchio</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Vecchio (rend. reale)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Nuovo Si (rend. reale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>98</v>
+      </c>
+      <c r="B34" s="16">
+        <f>(B$7*100+(100-A34)/B$8)/A34</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="B35" s="16">
+        <f>(B$7*100+(100-A35)/B$8)/A35</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B36" s="16">
+        <f>(B$7*100+(100-A36)/B$8)/A36</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="B37" s="16">
+        <f>(B$7*100+(100-A37)/B$8)/A37</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="B38" s="16">
+        <f>(B$7*100+(100-A38)/B$8)/A38</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="B39" s="16">
+        <f>(B$7*100+(100-A39)/B$8)/A39</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="B40" s="16">
+        <f>(B$7*100+(100-A40)/B$8)/A40</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="B41" s="16">
+        <f>(B$7*100+(100-A41)/B$8)/A41</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>B$14</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/simulatori/btp_si_compare_2026.xlsx
+++ b/simulatori/btp_si_compare_2026.xlsx
@@ -559,7 +559,6 @@
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -4919,7 +4918,7 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>101.83</v>
+        <v>101.32</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -4943,7 +4942,7 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>101.86</v>
+        <v>100.94</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
